--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="446">
   <si>
     <t>Semester 2 Specialist Timetable (Years 1-6) · colour-coded by specialist</t>
   </si>
@@ -2577,8 +2577,8 @@
 PE</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover T9
-(Dyer)</t>
+    <t xml:space="preserve">Cover LA1
+(Luca)</t>
   </si>
   <si>
     <t>Natalie Carter  ·  specialist (0.6; works Mon/Tue/Wed)</t>
@@ -2976,6 +2976,10 @@
 (class)</t>
   </si>
   <si>
+    <t xml:space="preserve">teacher
+(class)</t>
+  </si>
+  <si>
     <t>T10  ·  Kindy (Donna Campbell)</t>
   </si>
   <si>
@@ -3396,7 +3400,7 @@
     <t>| Caroline Parkin | PP | LA2 | 1 | 320m | 310m | -10m |</t>
   </si>
   <si>
-    <t>| Katie Digney | PP | LA1 | 0.8 | 256m | 250m | -6m |</t>
+    <t>| Katie Digney | PP | LA1 | 0.8 | 256m | 265m | +9m |</t>
   </si>
   <si>
     <t>| Nikki Luca | PP | LA1 | 0.4 | 128m | 105m | -23m |</t>
@@ -14438,8 +14442,8 @@
       <c r="E35" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>168</v>
+      <c r="F35" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14470,8 +14474,8 @@
       <c r="E37" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>268</v>
+      <c r="F37" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -15602,8 +15606,8 @@
       <c r="E107" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F107" s="22" t="s">
-        <v>285</v>
+      <c r="F107" s="9" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15634,8 +15638,8 @@
       <c r="E109" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>283</v>
+      <c r="F109" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -16605,12 +16609,12 @@
         <v>297</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -16867,7 +16871,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -17421,8 +17425,8 @@
       <c r="E35" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>168</v>
+      <c r="F35" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17453,8 +17457,8 @@
       <c r="E37" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>268</v>
+      <c r="F37" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -18585,8 +18589,8 @@
       <c r="E107" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F107" s="22" t="s">
-        <v>285</v>
+      <c r="F107" s="9" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18617,8 +18621,8 @@
       <c r="E109" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>283</v>
+      <c r="F109" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -19588,12 +19592,12 @@
         <v>297</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -19849,842 +19853,842 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="24" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="23" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="24" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="24" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="24" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="24" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="24" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="23" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="24" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="24" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="23" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="24" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="24" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="24" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="24" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="24" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="24" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="24" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="24" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="24" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="24" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="24" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="24" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="24" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="24" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="23" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="24" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="24" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="24" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="24" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="24" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="24" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="24" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="24" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="24" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="24" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="24" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="24" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="24" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="24" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="24" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="24" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="24" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="24" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="24" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="24" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="24" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="24" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4435" uniqueCount="447">
   <si>
     <t>Semester 2 Specialist Timetable (Years 1-6) · colour-coded by specialist</t>
   </si>
@@ -91,6 +91,23 @@
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
     <r>
       <rPr>
         <sz val="6"/>
@@ -104,7 +121,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA23 Visual Art</t>
+      <t>LA21 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -112,6 +129,88 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P2
+9:40-10:25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
   </si>
   <si>
@@ -121,7 +220,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 STEM</t>
+      <t>LA8 STEM</t>
     </r>
     <r>
       <rPr>
@@ -129,6 +228,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -143,7 +264,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Visual Art</t>
+      <t>LA19 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -152,15 +273,142 @@
       </rPr>
       <t xml:space="preserve">  Natalie Carter</t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Auslan</t>
+      <t>LA14 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -182,7 +430,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 Performing Arts</t>
+      <t>LA21 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -193,17 +441,161 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">P2
-9:40-10:25</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P3
+10:25-11:10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Visual Art</t>
+      <t>LA14 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -211,6 +603,67 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -225,7 +678,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 STEM</t>
+      <t>LA14 STEM</t>
     </r>
     <r>
       <rPr>
@@ -233,6 +686,222 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch
+11:10-11:50</t>
+  </si>
+  <si>
+    <t>Lunch (11:10-11:50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4
+11:50-12:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -242,7 +911,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 STEM</t>
+      <t>LA9 STEM</t>
     </r>
     <r>
       <rPr>
@@ -250,6 +919,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -264,7 +955,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA24 STEM</t>
+      <t>LA23 STEM</t>
     </r>
     <r>
       <rPr>
@@ -286,7 +977,46 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA19 Visual Art</t>
+      <t>LA7 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -308,7 +1038,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 Performing Arts</t>
+      <t>LA23 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -316,6 +1046,259 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P5
+12:35-1:20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -325,7 +1308,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 STEM</t>
+      <t>LA6 STEM</t>
     </r>
     <r>
       <rPr>
@@ -333,6 +1316,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -347,7 +1352,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 STEM</t>
+      <t>LA18 STEM</t>
     </r>
     <r>
       <rPr>
@@ -356,15 +1361,142 @@
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 PE</t>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 PE</t>
     </r>
     <r>
       <rPr>
@@ -386,7 +1518,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 PE</t>
+      <t>LA19 PE</t>
     </r>
     <r>
       <rPr>
@@ -408,7 +1540,7 @@
         <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 PE</t>
+      <t>LA20 PE</t>
     </r>
     <r>
       <rPr>
@@ -430,7 +1562,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 Auslan</t>
+      <t>LA7 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -452,7 +1584,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Performing Arts</t>
+      <t>LA24 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -469,7 +1601,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 Auslan</t>
+      <t>LA22 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -491,7 +1623,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 STEM</t>
+      <t>LA21 STEM</t>
     </r>
     <r>
       <rPr>
@@ -513,7 +1645,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Health</t>
+      <t>LA9 Health</t>
     </r>
     <r>
       <rPr>
@@ -524,8 +1656,15 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">P3
-10:25-11:10</t>
+    <t xml:space="preserve">Recess
+1:20-1:35</t>
+  </si>
+  <si>
+    <t>Recess (1:20-1:35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6
+1:35-2:35</t>
   </si>
   <si>
     <r>
@@ -534,7 +1673,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 STEM</t>
+      <t>LA22 STEM</t>
     </r>
     <r>
       <rPr>
@@ -542,6 +1681,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -551,7 +1712,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 STEM</t>
+      <t>LA6 STEM</t>
     </r>
     <r>
       <rPr>
@@ -559,6 +1720,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -573,7 +1756,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 Performing Arts</t>
+      <t>LA14 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -581,6 +1764,67 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -595,7 +1839,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA22 STEM</t>
+      <t>LA23 Health</t>
     </r>
     <r>
       <rPr>
@@ -603,6 +1847,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -617,7 +1883,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 Visual Art</t>
+      <t>LA9 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -631,17 +1897,83 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FF29A39A"/>
+        <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
+      <t>LA22 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -656,7 +1988,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Performing Arts</t>
+      <t>LA8 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -665,88 +1997,22 @@
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <color rgb="FF7E57C2"/>
+        <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
+      <t>LA19 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -761,7 +2027,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 PE</t>
+      <t>LA24 Health</t>
     </r>
     <r>
       <rPr>
@@ -770,1294 +2036,6 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch
-11:10-11:50</t>
-  </si>
-  <si>
-    <t>Lunch (11:10-11:50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4
-11:50-12:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P5
-12:35-1:20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Recess
-1:20-1:35</t>
-  </si>
-  <si>
-    <t>Recess (1:20-1:35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6
-1:35-2:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
   </si>
   <si>
     <t>Mon · whole school (specialist in colour, otherwise classroom teacher)</t>
@@ -2174,13 +2152,13 @@
     <t>P1 8:55-9:40</t>
   </si>
   <si>
-    <t>P2 9:40-10:25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Visual Art
 Natalie Carter</t>
   </si>
   <si>
+    <t>P2 9:40-10:25</t>
+  </si>
+  <si>
     <t xml:space="preserve">STEM
 Lis Lowndes</t>
   </si>
@@ -2537,30 +2515,30 @@
 STEM</t>
   </si>
   <si>
+    <t xml:space="preserve">LA23 (1)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA7 (5)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+STEM</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA22 (1)
 STEM</t>
   </si>
   <si>
-    <t xml:space="preserve">LA7 (5)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA19 (2)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-STEM</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA18 (2)
 STEM</t>
   </si>
@@ -3028,7 +3006,7 @@
     <t>2. Period 6 reconciliation</t>
   </si>
   <si>
-    <t>Period 6 lessons: 17 · 15 base class releases + 2 graduate Health. Some Health periods are deliberately off Period 6: the two leadership-release Healths (LA9, LA21) and two grad Healths (LA18, LA22) sit in Friday P2-P5 (Aaron Bell; P1 is the assembly), since Bell only has one P6 slot. Every Years 1-6 class still has a Period 6 release.</t>
+    <t>Period 6 lessons: 18 · 16 base class releases + 2 graduate Health. Some Health periods are deliberately off Period 6: the two leadership-release Healths (LA9, LA21) and two grad Healths (LA18, LA22) sit in Friday P2-P5 (Aaron Bell; P1 is the assembly), since Bell only has one P6 slot. Every Years 1-6 class still has a Period 6 release.</t>
   </si>
   <si>
     <t>| Day | Class | Subject | Teacher | Type |</t>
@@ -3040,6 +3018,9 @@
     <t>| Mon | LA17 | Visual Art | Natalie Carter | base release |</t>
   </si>
   <si>
+    <t>| Mon | LA22 | STEM | Lis Lowndes | base release |</t>
+  </si>
+  <si>
     <t>| Tue | LA14 | Performing Arts | Cheryl Peak | base release |</t>
   </si>
   <si>
@@ -3115,7 +3096,7 @@
     <t>4. Monday P0 and P1 vacancy</t>
   </si>
   <si>
-    <t>Monday P0 specialist lessons: 0. Monday P1 specialist lessons: 0. Clear of all specialist activity: PASS.</t>
+    <t>Monday P0 specialist lessons: 0. Monday P1 specialist lessons: 1. Clear of all specialist activity: FAIL.</t>
   </si>
   <si>
     <t>5. DOTT equity</t>
@@ -3133,7 +3114,7 @@
     <t>| Chantel Uhe | 0.4 teach | 12 | 50m | 108m | by design (office days carry her DOTT) |</t>
   </si>
   <si>
-    <t>| Lis Lowndes | 1.0 | 24 | 425m | 270m | OK |</t>
+    <t>| Lis Lowndes | 1.0 | 24 | 410m | 270m | OK |</t>
   </si>
   <si>
     <t>| Natalie Carter | 0.6 | 15 | 165m | 162m | OK |</t>
@@ -3193,7 +3174,7 @@
     <t>| LA21 | Jasper Sirr-Davis | OHS | 285m +45 lead | 270m | +15 collab top-up; +45 leadership (separate) |</t>
   </si>
   <si>
-    <t>| LA22 | Imogen Webb | grad | 330m | 270m | +60m (grad extra Health) |</t>
+    <t>| LA22 | Imogen Webb | grad | 345m | 270m | +75m (grad extra Health) |</t>
   </si>
   <si>
     <t>| LA23 | Ashlee Hutchings | grad | 345m | 270m | +75m (grad extra Health) |</t>
@@ -3340,10 +3321,10 @@
     <t>| LA21 | 0 | 0 | 2 | 2 | 3 | 3 (incl leadership) |</t>
   </si>
   <si>
-    <t>| LA22 | 0 | 2 | 1 | 2 | 2 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA23 | 2 | 1 | 2 | 1 | 1 | 2 |</t>
+    <t>| LA22 | 2 | 0 | 1 | 2 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA23 | 1 | 2 | 2 | 1 | 1 | 2 |</t>
   </si>
   <si>
     <t>| LA24 | 1 | 2 | 1 | 2 | 1 | 2 |</t>
@@ -3382,7 +3363,7 @@
     <t>STEM (rule 5): every STEM block is two back-to-back periods (consecutive period numbers, same day): PASS.</t>
   </si>
   <si>
-    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:7  P2:16  P3:18  P4:19  P5:19  P6:17. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
+    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:7  P2:16  P3:18  P4:18  P5:19  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
   </si>
   <si>
     <t>10. Pre-Primary &amp; Kindy DOTT ledger</t>
@@ -4048,7 +4029,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" ht="56" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" ht="40" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -4374,8 +4355,8 @@
       <c r="N4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="9" t="s">
-        <v>78</v>
+      <c r="O4" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="P4" s="9" t="s">
         <v>79</v>
@@ -4383,10 +4364,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>66</v>
@@ -4532,7 +4513,7 @@
         <v>72</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>74</v>
@@ -4546,8 +4527,8 @@
       <c r="N8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="11" t="s">
-        <v>83</v>
+      <c r="O8" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P8" s="9" t="s">
         <v>79</v>
@@ -4593,14 +4574,14 @@
       <c r="M9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>83</v>
       </c>
+      <c r="O9" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="P9" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4651,7 +4632,7 @@
         <v>71</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>73</v>
@@ -4665,8 +4646,8 @@
       <c r="M11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>77</v>
+      <c r="N11" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>78</v>
@@ -4838,8 +4819,8 @@
       <c r="N16" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O16" s="10" t="s">
-        <v>82</v>
+      <c r="O16" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P16" s="11" t="s">
         <v>83</v>
@@ -4847,7 +4828,7 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>65</v>
@@ -4877,7 +4858,7 @@
         <v>73</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>92</v>
@@ -4912,7 +4893,7 @@
         <v>91</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>70</v>
@@ -4935,11 +4916,11 @@
       <c r="M18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="P18" s="9" t="s">
         <v>79</v>
@@ -4975,7 +4956,7 @@
         <v>65</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>67</v>
@@ -5007,11 +4988,11 @@
       <c r="M20" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="N20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="P20" s="9" t="s">
         <v>79</v>
@@ -5040,7 +5021,7 @@
         <v>70</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>72</v>
@@ -5124,7 +5105,7 @@
         <v>74</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M23" s="9" t="s">
         <v>76</v>
@@ -5297,7 +5278,7 @@
         <v>75</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>77</v>
@@ -5311,7 +5292,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>65</v>
@@ -5379,7 +5360,7 @@
         <v>83</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>91</v>
@@ -5472,7 +5453,7 @@
         <v>76</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O32" s="13" t="s">
         <v>92</v>
@@ -5492,7 +5473,7 @@
         <v>91</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>94</v>
@@ -5567,7 +5548,7 @@
         <v>67</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>69</v>
@@ -5775,7 +5756,7 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>97</v>
@@ -6239,7 +6220,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>65</v>
@@ -6635,10 +6616,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>65</v>
@@ -6829,7 +6810,7 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>66</v>
@@ -6887,7 +6868,7 @@
         <v>66</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>66</v>
@@ -7023,7 +7004,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>67</v>
@@ -7104,7 +7085,7 @@
         <v>67</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>67</v>
@@ -7217,7 +7198,7 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>68</v>
@@ -7330,7 +7311,7 @@
         <v>68</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>68</v>
@@ -7411,7 +7392,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>69</v>
@@ -7437,7 +7418,7 @@
         <v>69</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>83</v>
@@ -7605,7 +7586,7 @@
     </row>
     <row r="65" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>70</v>
@@ -7634,7 +7615,7 @@
         <v>70</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>94</v>
@@ -7799,7 +7780,7 @@
     </row>
     <row r="77" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>71</v>
@@ -7877,7 +7858,7 @@
         <v>71</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>71</v>
@@ -7993,7 +7974,7 @@
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>72</v>
@@ -8100,7 +8081,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>72</v>
@@ -8187,7 +8168,7 @@
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>73</v>
@@ -8242,7 +8223,7 @@
         <v>86</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>73</v>
@@ -8381,13 +8362,13 @@
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>74</v>
@@ -8575,7 +8556,7 @@
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>83</v>
@@ -8685,7 +8666,7 @@
         <v>75</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>75</v>
@@ -8758,7 +8739,7 @@
         <v>76</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>76</v>
@@ -8769,7 +8750,7 @@
     </row>
     <row r="137" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>76</v>
@@ -8963,7 +8944,7 @@
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B149" s="9" t="s">
         <v>77</v>
@@ -8988,8 +8969,8 @@
       <c r="B150" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C150" s="11" t="s">
-        <v>83</v>
+      <c r="C150" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="D150" s="9" t="s">
         <v>77</v>
@@ -9020,11 +9001,11 @@
       <c r="B152" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C152" s="11" t="s">
-        <v>83</v>
+      <c r="C152" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>77</v>
@@ -9037,8 +9018,8 @@
       <c r="A153" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="9" t="s">
-        <v>77</v>
+      <c r="B153" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C153" s="9" t="s">
         <v>77</v>
@@ -9069,8 +9050,8 @@
       <c r="A155" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B155" s="9" t="s">
-        <v>77</v>
+      <c r="B155" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>77</v>
@@ -9139,11 +9120,11 @@
       <c r="A160" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B160" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C160" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="C160" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="D160" s="9" t="s">
         <v>78</v>
@@ -9157,7 +9138,7 @@
     </row>
     <row r="161" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B161" s="9" t="s">
         <v>78</v>
@@ -9182,8 +9163,8 @@
       <c r="B162" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C162" s="9" t="s">
-        <v>78</v>
+      <c r="C162" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D162" s="9" t="s">
         <v>78</v>
@@ -9211,11 +9192,11 @@
       <c r="A164" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C164" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="C164" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="D164" s="13" t="s">
         <v>92</v>
@@ -9231,8 +9212,8 @@
       <c r="A165" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B165" s="11" t="s">
-        <v>83</v>
+      <c r="B165" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="C165" s="9" t="s">
         <v>78</v>
@@ -9351,7 +9332,7 @@
     </row>
     <row r="173" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>79</v>
@@ -9426,7 +9407,7 @@
         <v>87</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>79</v>
@@ -9607,7 +9588,7 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>121</v>
@@ -9801,7 +9782,7 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>126</v>
@@ -9995,7 +9976,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>129</v>
@@ -10189,7 +10170,7 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>131</v>
@@ -10383,7 +10364,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>134</v>
@@ -10577,7 +10558,7 @@
     </row>
     <row r="65" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>138</v>
@@ -10771,7 +10752,7 @@
     </row>
     <row r="77" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>140</v>
@@ -10965,7 +10946,7 @@
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>142</v>
@@ -11159,7 +11140,7 @@
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>144</v>
@@ -11353,7 +11334,7 @@
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>149</v>
@@ -11547,7 +11528,7 @@
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B125" s="17" t="s">
         <v>135</v>
@@ -11741,7 +11722,7 @@
     </row>
     <row r="137" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>153</v>
@@ -11935,7 +11916,7 @@
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B149" s="9" t="s">
         <v>156</v>
@@ -11960,8 +11941,8 @@
       <c r="B150" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C150" s="17" t="s">
-        <v>135</v>
+      <c r="C150" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="D150" s="9" t="s">
         <v>156</v>
@@ -11992,8 +11973,8 @@
       <c r="B152" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C152" s="17" t="s">
-        <v>135</v>
+      <c r="C152" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="D152" s="18" t="s">
         <v>157</v>
@@ -12009,8 +11990,8 @@
       <c r="A153" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="9" t="s">
-        <v>156</v>
+      <c r="B153" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C153" s="9" t="s">
         <v>156</v>
@@ -12041,8 +12022,8 @@
       <c r="A155" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B155" s="9" t="s">
-        <v>156</v>
+      <c r="B155" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>156</v>
@@ -12111,11 +12092,11 @@
       <c r="A160" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B160" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C160" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="C160" s="17" t="s">
-        <v>121</v>
       </c>
       <c r="D160" s="9" t="s">
         <v>160</v>
@@ -12129,7 +12110,7 @@
     </row>
     <row r="161" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B161" s="9" t="s">
         <v>160</v>
@@ -12154,8 +12135,8 @@
       <c r="B162" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C162" s="9" t="s">
-        <v>160</v>
+      <c r="C162" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="D162" s="9" t="s">
         <v>160</v>
@@ -12183,11 +12164,11 @@
       <c r="A164" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B164" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C164" s="17" t="s">
         <v>135</v>
-      </c>
-      <c r="C164" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="D164" s="18" t="s">
         <v>157</v>
@@ -12203,8 +12184,8 @@
       <c r="A165" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B165" s="17" t="s">
-        <v>135</v>
+      <c r="B165" s="9" t="s">
+        <v>160</v>
       </c>
       <c r="C165" s="9" t="s">
         <v>160</v>
@@ -12323,7 +12304,7 @@
     </row>
     <row r="173" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>164</v>
@@ -12517,7 +12498,7 @@
     </row>
     <row r="185" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B185" s="20" t="s">
         <v>167</v>
@@ -12711,7 +12692,7 @@
     </row>
     <row r="197" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>179</v>
@@ -12765,20 +12746,20 @@
       <c r="A200" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B200" s="11" t="s">
-        <v>185</v>
+      <c r="B200" s="21" t="s">
+        <v>168</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>183</v>
       </c>
       <c r="D200" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E200" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E200" s="11" t="s">
+      <c r="F200" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="F200" s="11" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="201" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12786,19 +12767,19 @@
         <v>87</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>189</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E201" s="11" t="s">
         <v>190</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12817,8 +12798,8 @@
       <c r="A203" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B203" s="21" t="s">
-        <v>168</v>
+      <c r="B203" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>189</v>
@@ -12887,11 +12868,11 @@
       <c r="A208" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B208" s="21" t="s">
+      <c r="B208" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C208" s="21" t="s">
         <v>168</v>
-      </c>
-      <c r="C208" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>196</v>
@@ -12905,7 +12886,7 @@
     </row>
     <row r="209" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>197</v>
@@ -13099,7 +13080,7 @@
     </row>
     <row r="221" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B221" s="20" t="s">
         <v>169</v>
@@ -13293,7 +13274,7 @@
     </row>
     <row r="233" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B233" s="20" t="s">
         <v>169</v>
@@ -13487,7 +13468,7 @@
     </row>
     <row r="245" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B245" s="20" t="s">
         <v>169</v>
@@ -13681,7 +13662,7 @@
     </row>
     <row r="257" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B257" s="20" t="s">
         <v>169</v>
@@ -13968,7 +13949,7 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>264</v>
@@ -14162,7 +14143,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>266</v>
@@ -14356,7 +14337,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>268</v>
@@ -14550,7 +14531,7 @@
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>169</v>
@@ -14744,7 +14725,7 @@
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>271</v>
@@ -14938,7 +14919,7 @@
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
@@ -15132,7 +15113,7 @@
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>169</v>
@@ -15326,7 +15307,7 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>168</v>
@@ -15520,7 +15501,7 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>283</v>
@@ -15714,7 +15695,7 @@
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>287</v>
@@ -15908,7 +15889,7 @@
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>290</v>
@@ -16102,7 +16083,7 @@
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B139" s="20" t="s">
         <v>293</v>
@@ -16296,7 +16277,7 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>291</v>
@@ -16490,7 +16471,7 @@
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B163" s="20" t="s">
         <v>293</v>
@@ -16684,7 +16665,7 @@
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>288</v>
@@ -16951,7 +16932,7 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>264</v>
@@ -17145,7 +17126,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>266</v>
@@ -17339,7 +17320,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>268</v>
@@ -17533,7 +17514,7 @@
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>169</v>
@@ -17727,7 +17708,7 @@
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>271</v>
@@ -17921,7 +17902,7 @@
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
@@ -18115,7 +18096,7 @@
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>169</v>
@@ -18309,7 +18290,7 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>168</v>
@@ -18503,7 +18484,7 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>283</v>
@@ -18697,7 +18678,7 @@
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>287</v>
@@ -18891,7 +18872,7 @@
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>290</v>
@@ -19085,7 +19066,7 @@
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B139" s="20" t="s">
         <v>293</v>
@@ -19279,7 +19260,7 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>291</v>
@@ -19473,7 +19454,7 @@
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B163" s="20" t="s">
         <v>293</v>
@@ -19667,7 +19648,7 @@
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>288</v>
@@ -19845,7 +19826,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A168"/>
+  <dimension ref="A1:A169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -20037,38 +20018,38 @@
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="24" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
-        <v>336</v>
-      </c>
-    </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="23" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
@@ -20087,52 +20068,52 @@
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="24" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="23" t="s">
-        <v>343</v>
-      </c>
-    </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>302</v>
+      <c r="A51" s="23" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>344</v>
+        <v>302</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23" t="s">
-        <v>345</v>
-      </c>
-    </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>302</v>
+      <c r="A55" s="23" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="24" t="s">
+      <c r="A57" t="s">
         <v>347</v>
       </c>
     </row>
@@ -20177,23 +20158,23 @@
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="24" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="24" t="s">
+      <c r="A67" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="24" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
@@ -20267,38 +20248,38 @@
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="24" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="23" t="s">
-        <v>374</v>
-      </c>
-    </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="24" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="24" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
@@ -20332,28 +20313,28 @@
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="24" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="23" t="s">
-        <v>384</v>
-      </c>
-    </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="23" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="24" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
@@ -20437,32 +20418,32 @@
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" s="24" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="23" t="s">
-        <v>403</v>
-      </c>
-    </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>302</v>
+      <c r="A121" s="23" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>404</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="24" t="s">
+      <c r="A123" t="s">
         <v>405</v>
       </c>
     </row>
@@ -20547,32 +20528,32 @@
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="24" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="23" t="s">
-        <v>423</v>
-      </c>
-    </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>302</v>
+      <c r="A143" s="23" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>424</v>
+        <v>302</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="24" t="s">
+      <c r="A145" t="s">
         <v>425</v>
       </c>
     </row>
@@ -20607,7 +20588,7 @@
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="24" t="s">
         <v>432</v>
       </c>
     </row>
@@ -20618,37 +20599,37 @@
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="23" t="s">
-        <v>434</v>
-      </c>
-    </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>302</v>
+      <c r="A156" s="23" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>435</v>
+        <v>302</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="24" t="s">
+      <c r="A158" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="24" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="24" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
@@ -20687,8 +20668,13 @@
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="24" t="s">
         <v>445</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -466,10 +466,236 @@
     <r>
       <rPr>
         <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P3
+10:25-11:10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
       <t>LA15 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 PE</t>
     </r>
     <r>
       <rPr>
@@ -491,7 +717,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Health</t>
+      <t>LA16 PE</t>
     </r>
     <r>
       <rPr>
@@ -500,10 +726,122 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P3
-10:25-11:10</t>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch
+11:10-11:50</t>
+  </si>
+  <si>
+    <t>Lunch (11:10-11:50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4
+11:50-12:35</t>
   </si>
   <si>
     <r>
@@ -512,7 +850,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 STEM</t>
+      <t>LA15 STEM</t>
     </r>
     <r>
       <rPr>
@@ -520,6 +858,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -551,7 +911,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 Performing Arts</t>
+      <t>LA17 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -595,7 +955,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 Visual Art</t>
+      <t>LA7 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -631,10 +991,32 @@
     <r>
       <rPr>
         <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Performing Arts</t>
+      <t>LA23 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -656,7 +1038,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 Auslan</t>
+      <t>LA24 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -678,7 +1060,194 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 STEM</t>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P5
+12:35-1:20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 STEM</t>
     </r>
     <r>
       <rPr>
@@ -700,7 +1269,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 Visual Art</t>
+      <t>LA24 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -711,13 +1280,201 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 PE</t>
+      <t>LA18 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 PE</t>
     </r>
     <r>
       <rPr>
@@ -739,7 +1496,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 PE</t>
+      <t>LA19 PE</t>
     </r>
     <r>
       <rPr>
@@ -761,7 +1518,7 @@
         <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 PE</t>
+      <t>LA20 PE</t>
     </r>
     <r>
       <rPr>
@@ -783,7 +1540,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 Auslan</t>
+      <t>LA7 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -805,7 +1562,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA22 Performing Arts</t>
+      <t>LA24 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -822,7 +1579,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 Auslan</t>
+      <t>LA22 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -830,6 +1587,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -844,7 +1623,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 Health</t>
+      <t>LA9 Health</t>
     </r>
     <r>
       <rPr>
@@ -853,20 +1632,26 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Recess
+1:20-1:35</t>
+  </si>
+  <si>
+    <t>Recess (1:20-1:35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6
+1:35-2:35</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 STEM</t>
+      <t>LA22 STEM</t>
     </r>
     <r>
       <rPr>
@@ -875,26 +1660,20 @@
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch
-11:10-11:50</t>
-  </si>
-  <si>
-    <t>Lunch (11:10-11:50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4
-11:50-12:35</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 Visual Art</t>
+      <t>LA17 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -911,7 +1690,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 STEM</t>
+      <t>LA6 STEM</t>
     </r>
     <r>
       <rPr>
@@ -919,6 +1698,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -933,7 +1734,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 Performing Arts</t>
+      <t>LA14 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -941,6 +1742,67 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -955,7 +1817,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA23 STEM</t>
+      <t>LA23 Health</t>
     </r>
     <r>
       <rPr>
@@ -963,6 +1825,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -977,7 +1861,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 Visual Art</t>
+      <t>LA9 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -991,17 +1875,17 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FF29A39A"/>
+        <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
+      <t>LA22 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -1013,17 +1897,61 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FFD98A3D"/>
+        <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA22 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
+      <t>LA23 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -1038,7 +1966,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA23 Performing Arts</t>
+      <t>LA8 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -1047,66 +1975,22 @@
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <color rgb="FF7E57C2"/>
+        <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA24 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
+      <t>LA19 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -1121,7 +2005,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 PE</t>
+      <t>LA24 Health</t>
     </r>
     <r>
       <rPr>
@@ -1130,912 +2014,6 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P5
-12:35-1:20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Recess
-1:20-1:35</t>
-  </si>
-  <si>
-    <t>Recess (1:20-1:35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6
-1:35-2:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
   </si>
   <si>
     <t>Mon · whole school (specialist in colour, otherwise classroom teacher)</t>
@@ -2152,6 +2130,10 @@
     <t>P1 8:55-9:40</t>
   </si>
   <si>
+    <t xml:space="preserve">STEM
+Lis Lowndes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Visual Art
 Natalie Carter</t>
   </si>
@@ -2159,10 +2141,6 @@
     <t>P2 9:40-10:25</t>
   </si>
   <si>
-    <t xml:space="preserve">STEM
-Lis Lowndes</t>
-  </si>
-  <si>
     <t>P3 10:25-11:10</t>
   </si>
   <si>
@@ -2491,6 +2469,10 @@
     <t>Lis Lowndes  ·  specialist (1.0; works Mon/Tue/Wed/Thu/Fri)</t>
   </si>
   <si>
+    <t xml:space="preserve">LA20 (2)
+STEM</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA24 (1)
 STEM</t>
   </si>
@@ -2499,10 +2481,6 @@
 STEM/PE team</t>
   </si>
   <si>
-    <t xml:space="preserve">LA20 (2)
-STEM</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA14 (3/4)
 STEM</t>
   </si>
@@ -2511,6 +2489,10 @@
 PE</t>
   </si>
   <si>
+    <t xml:space="preserve">Cover LA1
+(Luca)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA15 (3)
 STEM</t>
   </si>
@@ -2555,10 +2537,6 @@
 PE</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover LA1
-(Luca)</t>
-  </si>
-  <si>
     <t>Natalie Carter  ·  specialist (0.6; works Mon/Tue/Wed)</t>
   </si>
   <si>
@@ -3096,7 +3074,7 @@
     <t>4. Monday P0 and P1 vacancy</t>
   </si>
   <si>
-    <t>Monday P0 specialist lessons: 0. Monday P1 specialist lessons: 1. Clear of all specialist activity: FAIL.</t>
+    <t>Monday P0 specialist lessons: 0. Monday P1 specialist lessons: 2. Clear of all specialist activity: FAIL.</t>
   </si>
   <si>
     <t>5. DOTT equity</t>
@@ -3300,7 +3278,7 @@
     <t>| LA14 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
-    <t>| LA15 | 0 | 0 | 2 | 2 | 2 | 2 |</t>
+    <t>| LA15 | 2 | 0 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA16 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
@@ -3363,7 +3341,7 @@
     <t>STEM (rule 5): every STEM block is two back-to-back periods (consecutive period numbers, same day): PASS.</t>
   </si>
   <si>
-    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:7  P2:16  P3:18  P4:18  P5:19  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
+    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:8  P2:15  P3:17  P4:19  P5:19  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
   </si>
   <si>
     <t>10. Pre-Primary &amp; Kindy DOTT ledger</t>
@@ -3384,7 +3362,7 @@
     <t>| Katie Digney | PP | LA1 | 0.8 | 256m | 265m | +9m |</t>
   </si>
   <si>
-    <t>| Nikki Luca | PP | LA1 | 0.4 | 128m | 105m | -23m |</t>
+    <t>| Nikki Luca | PP | LA1 | 0.4 | 128m | 135m | +7m |</t>
   </si>
   <si>
     <t>| Kelly Duggan | Kindy | LA4 | 0.8 | 256m | 260m | +4m |</t>
@@ -3496,12 +3474,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD98A3D"/>
+        <fgColor rgb="FF1F8A82"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8A82"/>
+        <fgColor rgb="FFD98A3D"/>
       </patternFill>
     </fill>
     <fill>
@@ -4346,8 +4324,8 @@
       <c r="K4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>75</v>
+      <c r="L4" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="M4" s="9" t="s">
         <v>76</v>
@@ -4355,8 +4333,8 @@
       <c r="N4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="10" t="s">
-        <v>81</v>
+      <c r="O4" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="P4" s="9" t="s">
         <v>79</v>
@@ -4364,10 +4342,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>66</v>
@@ -4396,8 +4374,8 @@
       <c r="K5" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>83</v>
+      <c r="L5" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="M5" s="9" t="s">
         <v>76</v>
@@ -4431,8 +4409,8 @@
       <c r="F6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>70</v>
+      <c r="G6" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>71</v>
@@ -4446,8 +4424,8 @@
       <c r="K6" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>83</v>
+      <c r="L6" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>76</v>
@@ -4503,8 +4481,8 @@
       <c r="F8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>70</v>
+      <c r="G8" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>71</v>
@@ -4512,8 +4490,8 @@
       <c r="I8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>81</v>
+      <c r="J8" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>74</v>
@@ -4574,14 +4552,14 @@
       <c r="M9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="11" t="s">
-        <v>83</v>
+      <c r="N9" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P9" s="10" t="s">
-        <v>81</v>
+      <c r="P9" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4631,8 +4609,8 @@
       <c r="H11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>81</v>
+      <c r="I11" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>73</v>
@@ -4646,8 +4624,8 @@
       <c r="M11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N11" s="11" t="s">
-        <v>83</v>
+      <c r="N11" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>78</v>
@@ -4822,13 +4800,13 @@
       <c r="O16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>83</v>
+      <c r="P16" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>65</v>
@@ -4857,8 +4835,8 @@
       <c r="J17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>81</v>
+      <c r="K17" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>92</v>
@@ -4872,8 +4850,8 @@
       <c r="O17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P17" s="11" t="s">
-        <v>83</v>
+      <c r="P17" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4892,8 +4870,8 @@
       <c r="E18" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>81</v>
+      <c r="F18" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>70</v>
@@ -4919,8 +4897,8 @@
       <c r="N18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O18" s="11" t="s">
-        <v>83</v>
+      <c r="O18" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="P18" s="9" t="s">
         <v>79</v>
@@ -4955,8 +4933,8 @@
       <c r="B20" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>81</v>
+      <c r="C20" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>67</v>
@@ -4991,8 +4969,8 @@
       <c r="N20" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O20" s="11" t="s">
-        <v>83</v>
+      <c r="O20" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="P20" s="9" t="s">
         <v>79</v>
@@ -5020,14 +4998,14 @@
       <c r="G21" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>81</v>
+      <c r="H21" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>83</v>
+      <c r="J21" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>74</v>
@@ -5098,14 +5076,14 @@
       <c r="I23" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="11" t="s">
-        <v>83</v>
+      <c r="J23" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L23" s="10" t="s">
-        <v>81</v>
+      <c r="L23" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="M23" s="9" t="s">
         <v>76</v>
@@ -5277,8 +5255,8 @@
       <c r="L28" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="10" t="s">
-        <v>81</v>
+      <c r="M28" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>77</v>
@@ -5292,7 +5270,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>65</v>
@@ -5306,8 +5284,8 @@
       <c r="E29" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>83</v>
+      <c r="F29" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>70</v>
@@ -5356,11 +5334,11 @@
       <c r="E30" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" s="10" t="s">
+      <c r="F30" s="10" t="s">
         <v>81</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>91</v>
@@ -5443,8 +5421,8 @@
       <c r="J32" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K32" s="11" t="s">
-        <v>83</v>
+      <c r="K32" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>75</v>
@@ -5452,8 +5430,8 @@
       <c r="M32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N32" s="10" t="s">
-        <v>81</v>
+      <c r="N32" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="O32" s="13" t="s">
         <v>92</v>
@@ -5472,8 +5450,8 @@
       <c r="C33" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>81</v>
+      <c r="D33" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>94</v>
@@ -5493,8 +5471,8 @@
       <c r="J33" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="K33" s="11" t="s">
-        <v>83</v>
+      <c r="K33" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>75</v>
@@ -5547,8 +5525,8 @@
       <c r="D35" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>81</v>
+      <c r="E35" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>69</v>
@@ -5577,7 +5555,7 @@
       <c r="N35" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="10" t="s">
         <v>95</v>
       </c>
       <c r="P35" s="9" t="s">
@@ -5756,9 +5734,9 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -5811,7 +5789,7 @@
       <c r="B42" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="10" t="s">
         <v>97</v>
       </c>
       <c r="D42" s="9" t="s">
@@ -5892,7 +5870,7 @@
       <c r="E44" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="10" t="s">
         <v>97</v>
       </c>
       <c r="G44" s="15" t="s">
@@ -5954,7 +5932,7 @@
       <c r="I45" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="10" t="s">
         <v>97</v>
       </c>
       <c r="K45" s="15" t="s">
@@ -6038,7 +6016,7 @@
       <c r="M47" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N47" s="11" t="s">
+      <c r="N47" s="10" t="s">
         <v>97</v>
       </c>
       <c r="O47" s="15" t="s">
@@ -6220,7 +6198,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>65</v>
@@ -6237,8 +6215,8 @@
       <c r="F53" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G53" s="11" t="s">
-        <v>83</v>
+      <c r="G53" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H53" s="9" t="s">
         <v>71</v>
@@ -6287,8 +6265,8 @@
       <c r="F54" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G54" s="11" t="s">
-        <v>83</v>
+      <c r="G54" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>71</v>
@@ -6377,8 +6355,8 @@
       <c r="L56" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M56" s="11" t="s">
-        <v>83</v>
+      <c r="M56" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="N56" s="15" t="s">
         <v>102</v>
@@ -6427,8 +6405,8 @@
       <c r="L57" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M57" s="11" t="s">
-        <v>83</v>
+      <c r="M57" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="N57" s="13" t="s">
         <v>101</v>
@@ -6616,10 +6594,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>65</v>
@@ -6627,7 +6605,7 @@
       <c r="D5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -6810,7 +6788,7 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>66</v>
@@ -6841,7 +6819,7 @@
       <c r="D18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F18" s="9" t="s">
@@ -6867,8 +6845,8 @@
       <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>81</v>
+      <c r="C20" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>66</v>
@@ -7004,7 +6982,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>67</v>
@@ -7084,8 +7062,8 @@
       <c r="C33" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>81</v>
+      <c r="D33" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>67</v>
@@ -7198,7 +7176,7 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>68</v>
@@ -7310,8 +7288,8 @@
       <c r="C47" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="10" t="s">
-        <v>81</v>
+      <c r="D47" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>68</v>
@@ -7392,7 +7370,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>69</v>
@@ -7400,8 +7378,8 @@
       <c r="C53" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D53" s="11" t="s">
-        <v>83</v>
+      <c r="D53" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>94</v>
@@ -7417,11 +7395,11 @@
       <c r="B54" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>69</v>
@@ -7455,7 +7433,7 @@
       <c r="D56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F56" s="9" t="s">
@@ -7586,7 +7564,7 @@
     </row>
     <row r="65" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>70</v>
@@ -7600,28 +7578,28 @@
       <c r="E65" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F65" s="11" t="s">
-        <v>83</v>
+      <c r="F65" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>70</v>
+      <c r="B66" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D66" s="10" t="s">
-        <v>81</v>
+      <c r="D66" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F66" s="11" t="s">
-        <v>83</v>
+      <c r="F66" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7640,8 +7618,8 @@
       <c r="A68" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>70</v>
+      <c r="B68" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>70</v>
@@ -7780,7 +7758,7 @@
     </row>
     <row r="77" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>71</v>
@@ -7857,8 +7835,8 @@
       <c r="B81" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>81</v>
+      <c r="C81" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>71</v>
@@ -7974,7 +7952,7 @@
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>72</v>
@@ -8080,8 +8058,8 @@
       <c r="A95" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>81</v>
+      <c r="B95" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>72</v>
@@ -8168,7 +8146,7 @@
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>73</v>
@@ -8222,8 +8200,8 @@
       <c r="A104" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>81</v>
+      <c r="B104" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>73</v>
@@ -8245,13 +8223,13 @@
       <c r="B105" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>83</v>
+      <c r="C105" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E105" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F105" s="9" t="s">
@@ -8277,8 +8255,8 @@
       <c r="B107" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>83</v>
+      <c r="C107" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>73</v>
@@ -8362,13 +8340,13 @@
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>81</v>
+      <c r="C113" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>74</v>
@@ -8422,8 +8400,8 @@
       <c r="C116" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D116" s="11" t="s">
-        <v>83</v>
+      <c r="D116" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="E116" s="13" t="s">
         <v>92</v>
@@ -8442,8 +8420,8 @@
       <c r="C117" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D117" s="11" t="s">
-        <v>83</v>
+      <c r="D117" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>98</v>
@@ -8538,8 +8516,8 @@
       <c r="A124" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="9" t="s">
-        <v>75</v>
+      <c r="B124" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C124" s="9" t="s">
         <v>75</v>
@@ -8556,10 +8534,10 @@
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B125" s="11" t="s">
         <v>83</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>92</v>
@@ -8578,8 +8556,8 @@
       <c r="A126" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B126" s="11" t="s">
-        <v>83</v>
+      <c r="B126" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="C126" s="9" t="s">
         <v>75</v>
@@ -8665,8 +8643,8 @@
       <c r="B131" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>81</v>
+      <c r="C131" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>75</v>
@@ -8738,8 +8716,8 @@
       <c r="C136" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D136" s="10" t="s">
-        <v>81</v>
+      <c r="D136" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>76</v>
@@ -8750,7 +8728,7 @@
     </row>
     <row r="137" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>76</v>
@@ -8816,8 +8794,8 @@
       <c r="E140" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F140" s="11" t="s">
-        <v>83</v>
+      <c r="F140" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="141" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8836,8 +8814,8 @@
       <c r="E141" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F141" s="11" t="s">
-        <v>83</v>
+      <c r="F141" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8944,7 +8922,7 @@
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B149" s="9" t="s">
         <v>77</v>
@@ -9004,8 +8982,8 @@
       <c r="C152" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D152" s="10" t="s">
-        <v>81</v>
+      <c r="D152" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>77</v>
@@ -9018,8 +8996,8 @@
       <c r="A153" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="11" t="s">
-        <v>83</v>
+      <c r="B153" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C153" s="9" t="s">
         <v>77</v>
@@ -9050,8 +9028,8 @@
       <c r="A155" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B155" s="11" t="s">
-        <v>83</v>
+      <c r="B155" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>77</v>
@@ -9059,7 +9037,7 @@
       <c r="D155" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E155" s="11" t="s">
+      <c r="E155" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F155" s="9" t="s">
@@ -9120,8 +9098,8 @@
       <c r="A160" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B160" s="10" t="s">
-        <v>81</v>
+      <c r="B160" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C160" s="9" t="s">
         <v>78</v>
@@ -9138,7 +9116,7 @@
     </row>
     <row r="161" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B161" s="9" t="s">
         <v>78</v>
@@ -9163,8 +9141,8 @@
       <c r="B162" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C162" s="11" t="s">
-        <v>83</v>
+      <c r="C162" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="D162" s="9" t="s">
         <v>78</v>
@@ -9195,8 +9173,8 @@
       <c r="B164" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C164" s="11" t="s">
-        <v>83</v>
+      <c r="C164" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="D164" s="13" t="s">
         <v>92</v>
@@ -9250,7 +9228,7 @@
       <c r="C167" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D167" s="11" t="s">
+      <c r="D167" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E167" s="15" t="s">
@@ -9317,8 +9295,8 @@
       <c r="B172" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C172" s="11" t="s">
-        <v>83</v>
+      <c r="C172" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>79</v>
@@ -9332,13 +9310,13 @@
     </row>
     <row r="173" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C173" s="11" t="s">
-        <v>83</v>
+      <c r="C173" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>79</v>
@@ -9406,8 +9384,8 @@
       <c r="A177" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B177" s="10" t="s">
-        <v>81</v>
+      <c r="B177" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>79</v>
@@ -9588,7 +9566,7 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>121</v>
@@ -9782,7 +9760,7 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>126</v>
@@ -9976,7 +9954,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>129</v>
@@ -10170,7 +10148,7 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>131</v>
@@ -10364,7 +10342,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>134</v>
@@ -10558,7 +10536,7 @@
     </row>
     <row r="65" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>138</v>
@@ -10572,16 +10550,16 @@
       <c r="E65" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F65" s="17" t="s">
-        <v>135</v>
+      <c r="F65" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>138</v>
+      <c r="B66" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>138</v>
@@ -10592,8 +10570,8 @@
       <c r="E66" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F66" s="17" t="s">
-        <v>135</v>
+      <c r="F66" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10612,8 +10590,8 @@
       <c r="A68" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>138</v>
+      <c r="B68" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>138</v>
@@ -10752,7 +10730,7 @@
     </row>
     <row r="77" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>140</v>
@@ -10946,7 +10924,7 @@
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>142</v>
@@ -11140,7 +11118,7 @@
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>144</v>
@@ -11334,7 +11312,7 @@
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>149</v>
@@ -11510,8 +11488,8 @@
       <c r="A124" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="9" t="s">
-        <v>151</v>
+      <c r="B124" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C124" s="9" t="s">
         <v>151</v>
@@ -11528,7 +11506,7 @@
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B125" s="17" t="s">
         <v>135</v>
@@ -11550,8 +11528,8 @@
       <c r="A126" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B126" s="17" t="s">
-        <v>135</v>
+      <c r="B126" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="C126" s="9" t="s">
         <v>151</v>
@@ -11722,7 +11700,7 @@
     </row>
     <row r="137" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>153</v>
@@ -11916,7 +11894,7 @@
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B149" s="9" t="s">
         <v>156</v>
@@ -12110,7 +12088,7 @@
     </row>
     <row r="161" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B161" s="9" t="s">
         <v>160</v>
@@ -12304,7 +12282,7 @@
     </row>
     <row r="173" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>164</v>
@@ -12498,7 +12476,7 @@
     </row>
     <row r="185" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B185" s="20" t="s">
         <v>167</v>
@@ -12674,17 +12652,17 @@
       <c r="A196" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B196" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C196" s="11" t="s">
+      <c r="B196" s="10" t="s">
         <v>177</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="D196" s="21" t="s">
         <v>168</v>
       </c>
       <c r="E196" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F196" s="21" t="s">
         <v>168</v>
@@ -12692,21 +12670,21 @@
     </row>
     <row r="197" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B197" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C197" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B197" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="D197" s="11" t="s">
+      <c r="C197" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D197" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E197" s="11" t="s">
+      <c r="E197" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F197" s="11" t="s">
+      <c r="F197" s="22" t="s">
         <v>182</v>
       </c>
     </row>
@@ -12714,19 +12692,19 @@
       <c r="A198" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B198" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C198" s="11" t="s">
+      <c r="B198" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D198" s="11" t="s">
+      <c r="C198" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D198" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E198" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F198" s="11" t="s">
+      <c r="E198" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F198" s="22" t="s">
         <v>182</v>
       </c>
     </row>
@@ -12746,40 +12724,40 @@
       <c r="A200" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B200" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C200" s="11" t="s">
+      <c r="B200" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D200" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E200" s="11" t="s">
+      <c r="C200" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D200" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F200" s="11" t="s">
+      <c r="E200" s="10" t="s">
         <v>187</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="201" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B201" s="11" t="s">
+      <c r="B201" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F201" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="C201" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D201" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E201" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F201" s="11" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12798,20 +12776,20 @@
       <c r="A203" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B203" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="C203" s="11" t="s">
+      <c r="B203" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D203" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="E203" s="11" t="s">
+      <c r="C203" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D203" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F203" s="22" t="s">
+      <c r="E203" s="10" t="s">
         <v>193</v>
+      </c>
+      <c r="F203" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -12868,13 +12846,13 @@
       <c r="A208" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B208" s="10" t="s">
+      <c r="B208" s="11" t="s">
         <v>195</v>
       </c>
       <c r="C208" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="11" t="s">
         <v>196</v>
       </c>
       <c r="E208" s="20" t="s">
@@ -12886,12 +12864,12 @@
     </row>
     <row r="209" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B209" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B209" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C209" s="10" t="s">
+      <c r="C209" s="11" t="s">
         <v>198</v>
       </c>
       <c r="D209" s="18" t="s">
@@ -12911,10 +12889,10 @@
       <c r="B210" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C210" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" s="11" t="s">
         <v>202</v>
       </c>
       <c r="E210" s="20" t="s">
@@ -12940,13 +12918,13 @@
       <c r="A212" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B212" s="10" t="s">
+      <c r="B212" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C212" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="D212" s="11" t="s">
         <v>205</v>
       </c>
       <c r="E212" s="20" t="s">
@@ -12960,13 +12938,13 @@
       <c r="A213" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B213" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="C213" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="11" t="s">
         <v>208</v>
       </c>
       <c r="E213" s="20" t="s">
@@ -12992,13 +12970,13 @@
       <c r="A215" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B215" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C215" s="10" t="s">
+      <c r="C215" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="D215" s="11" t="s">
         <v>211</v>
       </c>
       <c r="E215" s="20" t="s">
@@ -13080,7 +13058,7 @@
     </row>
     <row r="221" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B221" s="20" t="s">
         <v>169</v>
@@ -13274,7 +13252,7 @@
     </row>
     <row r="233" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B233" s="20" t="s">
         <v>169</v>
@@ -13460,7 +13438,7 @@
         <v>169</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F244" s="21" t="s">
         <v>168</v>
@@ -13468,7 +13446,7 @@
     </row>
     <row r="245" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B245" s="20" t="s">
         <v>169</v>
@@ -13662,7 +13640,7 @@
     </row>
     <row r="257" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B257" s="20" t="s">
         <v>169</v>
@@ -13949,7 +13927,7 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>264</v>
@@ -14143,7 +14121,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>266</v>
@@ -14337,7 +14315,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>268</v>
@@ -14531,7 +14509,7 @@
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>169</v>
@@ -14545,8 +14523,8 @@
       <c r="E43" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>268</v>
+      <c r="F43" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14565,8 +14543,8 @@
       <c r="E44" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>268</v>
+      <c r="F44" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14649,8 +14627,8 @@
       <c r="E49" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F49" s="21" t="s">
-        <v>168</v>
+      <c r="F49" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -14725,7 +14703,7 @@
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>271</v>
@@ -14919,7 +14897,7 @@
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
@@ -15113,7 +15091,7 @@
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>169</v>
@@ -15307,7 +15285,7 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>168</v>
@@ -15501,7 +15479,7 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>283</v>
@@ -15515,8 +15493,8 @@
       <c r="E103" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>284</v>
+      <c r="F103" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15535,8 +15513,8 @@
       <c r="E104" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F104" s="9" t="s">
-        <v>284</v>
+      <c r="F104" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15619,8 +15597,8 @@
       <c r="E109" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="22" t="s">
-        <v>285</v>
+      <c r="F109" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -15695,7 +15673,7 @@
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>287</v>
@@ -15889,7 +15867,7 @@
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>290</v>
@@ -16083,7 +16061,7 @@
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B139" s="20" t="s">
         <v>293</v>
@@ -16277,7 +16255,7 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>291</v>
@@ -16471,7 +16449,7 @@
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B163" s="20" t="s">
         <v>293</v>
@@ -16665,7 +16643,7 @@
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>288</v>
@@ -16932,7 +16910,7 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>264</v>
@@ -17126,7 +17104,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>266</v>
@@ -17320,7 +17298,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>268</v>
@@ -17514,7 +17492,7 @@
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>169</v>
@@ -17528,8 +17506,8 @@
       <c r="E43" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>268</v>
+      <c r="F43" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17548,8 +17526,8 @@
       <c r="E44" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>268</v>
+      <c r="F44" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17632,8 +17610,8 @@
       <c r="E49" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F49" s="21" t="s">
-        <v>168</v>
+      <c r="F49" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -17708,7 +17686,7 @@
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>271</v>
@@ -17902,7 +17880,7 @@
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
@@ -18096,7 +18074,7 @@
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>169</v>
@@ -18290,7 +18268,7 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>168</v>
@@ -18484,7 +18462,7 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>283</v>
@@ -18498,8 +18476,8 @@
       <c r="E103" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>284</v>
+      <c r="F103" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18518,8 +18496,8 @@
       <c r="E104" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F104" s="9" t="s">
-        <v>284</v>
+      <c r="F104" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18602,8 +18580,8 @@
       <c r="E109" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="22" t="s">
-        <v>285</v>
+      <c r="F109" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -18678,7 +18656,7 @@
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>287</v>
@@ -18872,7 +18850,7 @@
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>290</v>
@@ -19066,7 +19044,7 @@
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B139" s="20" t="s">
         <v>293</v>
@@ -19260,7 +19238,7 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>291</v>
@@ -19454,7 +19432,7 @@
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B163" s="20" t="s">
         <v>293</v>
@@ -19648,7 +19626,7 @@
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>288</v>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -79,10 +79,32 @@
     <r>
       <rPr>
         <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA24 STEM</t>
+      <t>LA18 STEM</t>
     </r>
     <r>
       <rPr>
@@ -90,6 +112,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -118,27 +162,49 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FFD98A3D"/>
+        <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
+      <t>LA6 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Auslan</t>
+      <t>LA8 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -160,7 +226,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 Performing Arts</t>
+      <t>LA24 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -175,13 +241,35 @@
 9:40-10:25</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Visual Art</t>
+      <t>LA21 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -189,6 +277,45 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -203,7 +330,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 STEM</t>
+      <t>LA18 STEM</t>
     </r>
     <r>
       <rPr>
@@ -211,6 +338,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -220,7 +369,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 STEM</t>
+      <t>LA17 STEM</t>
     </r>
     <r>
       <rPr>
@@ -236,13 +385,222 @@
       <t xml:space="preserve">
 </t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
+      <t>LA6 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
       <t>LA24 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P3
+10:25-11:10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 STEM</t>
     </r>
     <r>
       <rPr>
@@ -264,7 +622,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA19 Visual Art</t>
+      <t>LA15 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -272,6 +630,23 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
     </r>
     <r>
       <rPr>
@@ -286,7 +661,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 Performing Arts</t>
+      <t>LA16 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -294,6 +669,50 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -303,7 +722,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 STEM</t>
+      <t>LA16 STEM</t>
     </r>
     <r>
       <rPr>
@@ -311,6 +730,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
     </r>
     <r>
       <rPr>
@@ -325,7 +766,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 STEM</t>
+      <t>LA20 STEM</t>
     </r>
     <r>
       <rPr>
@@ -333,6 +774,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -342,7 +805,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 PE</t>
+      <t>LA7 PE</t>
     </r>
     <r>
       <rPr>
@@ -364,7 +827,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 PE</t>
+      <t>LA16 PE</t>
     </r>
     <r>
       <rPr>
@@ -386,7 +849,7 @@
         <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 PE</t>
+      <t>LA17 PE</t>
     </r>
     <r>
       <rPr>
@@ -408,7 +871,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 Auslan</t>
+      <t>LA21 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -430,7 +893,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Performing Arts</t>
+      <t>LA14 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -447,7 +910,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 Auslan</t>
+      <t>LA23 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -455,6 +918,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -480,8 +965,15 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">P3
-10:25-11:10</t>
+    <t xml:space="preserve">Lunch
+11:10-11:50</t>
+  </si>
+  <si>
+    <t>Lunch (11:10-11:50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4
+11:50-12:35</t>
   </si>
   <si>
     <r>
@@ -490,7 +982,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 STEM</t>
+      <t>LA23 STEM</t>
     </r>
     <r>
       <rPr>
@@ -498,6 +990,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -529,7 +1043,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 Performing Arts</t>
+      <t>LA21 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -551,7 +1065,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA23 STEM</t>
+      <t>LA14 STEM</t>
     </r>
     <r>
       <rPr>
@@ -573,7 +1087,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 Visual Art</t>
+      <t>LA20 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -609,10 +1123,32 @@
     <r>
       <rPr>
         <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Performing Arts</t>
+      <t>LA23 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -634,7 +1170,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 Auslan</t>
+      <t>LA24 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -656,7 +1192,194 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 STEM</t>
+      <t>LA20 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P5
+12:35-1:20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 STEM</t>
     </r>
     <r>
       <rPr>
@@ -678,7 +1401,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 Visual Art</t>
+      <t>LA14 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -689,13 +1412,113 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 PE</t>
+      <t>LA22 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 PE</t>
     </r>
     <r>
       <rPr>
@@ -717,7 +1540,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 PE</t>
+      <t>LA19 PE</t>
     </r>
     <r>
       <rPr>
@@ -739,7 +1562,7 @@
         <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 PE</t>
+      <t>LA20 PE</t>
     </r>
     <r>
       <rPr>
@@ -761,7 +1584,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 Auslan</t>
+      <t>LA17 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -797,10 +1620,32 @@
     <r>
       <rPr>
         <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 Auslan</t>
+      <t>LA18 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -808,6 +1653,283 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Recess
+1:20-1:35</t>
+  </si>
+  <si>
+    <t>Recess (1:20-1:35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6
+1:35-2:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -822,7 +1944,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 Health</t>
+      <t>LA23 PE</t>
     </r>
     <r>
       <rPr>
@@ -831,34 +1953,6 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch
-11:10-11:50</t>
-  </si>
-  <si>
-    <t>Lunch (11:10-11:50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4
-11:50-12:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
     <r>
       <rPr>
         <sz val="6"/>
@@ -869,34 +1963,39 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FFD98A3D"/>
+        <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
+      <t>LA24 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <color rgb="FF29A39A"/>
+        <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
+      <t>LA16 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -911,7 +2010,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 Performing Arts</t>
+      <t>LA18 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -920,103 +2019,15 @@
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA23 Performing Arts</t>
+      <t>LA20 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -1024,67 +2035,6 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -1099,7 +2049,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 PE</t>
+      <t>LA23 Health</t>
     </r>
     <r>
       <rPr>
@@ -1108,912 +2058,6 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P5
-12:35-1:20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Recess
-1:20-1:35</t>
-  </si>
-  <si>
-    <t>Recess (1:20-1:35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6
-1:35-2:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
   </si>
   <si>
     <t>Mon · whole school (specialist in colour, otherwise classroom teacher)</t>
@@ -2130,6 +2174,9 @@
     <t>P1 8:55-9:40</t>
   </si>
   <si>
+    <t>P2 9:40-10:25</t>
+  </si>
+  <si>
     <t xml:space="preserve">STEM
 Lis Lowndes</t>
   </si>
@@ -2138,9 +2185,6 @@
 Natalie Carter</t>
   </si>
   <si>
-    <t>P2 9:40-10:25</t>
-  </si>
-  <si>
     <t>P3 10:25-11:10</t>
   </si>
   <si>
@@ -2157,6 +2201,10 @@
   </si>
   <si>
     <t>P6 1:35-2:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health
+Lis Lowndes</t>
   </si>
   <si>
     <t>Tue · whole school (specialist in colour, otherwise classroom teacher)</t>
@@ -2177,10 +2225,6 @@
 Rachel Walker</t>
   </si>
   <si>
-    <t xml:space="preserve">Health
-Lis Lowndes</t>
-  </si>
-  <si>
     <t>Thu · whole school (specialist in colour, otherwise classroom teacher)</t>
   </si>
   <si>
@@ -2199,14 +2243,14 @@
     <t>Fri · whole school (specialist in colour, otherwise classroom teacher)</t>
   </si>
   <si>
+    <t xml:space="preserve">Health
+Aaron Bell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auslan
 Cheryl Peak</t>
   </si>
   <si>
-    <t xml:space="preserve">Health
-Aaron Bell</t>
-  </si>
-  <si>
     <t>LA6  (Year 5/6 · John Dunbar)</t>
   </si>
   <si>
@@ -2260,7 +2304,30 @@
   </si>
   <si>
     <t xml:space="preserve">DOTT (release)
+Performing Arts · Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration
+Y5-6 meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOTT (release)
+PE · Lowndes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOTT (release)
 Auslan · Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOTT (release)
+STEM · Uhe</t>
+  </si>
+  <si>
+    <t>Nicola Pigott  ·  classroom teacher (LA7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA7
+own class</t>
   </si>
   <si>
     <t xml:space="preserve">DOTT (release)
@@ -2268,25 +2335,6 @@
   </si>
   <si>
     <t xml:space="preserve">Collaboration
-Y5-6 meeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOTT (release)
-Performing Arts · Peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOTT (release)
-STEM · Uhe</t>
-  </si>
-  <si>
-    <t>Nicola Pigott  ·  classroom teacher (LA7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7
-own class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaboration
 Y4-5 meeting</t>
   </si>
   <si>
@@ -2297,6 +2345,10 @@
 own class</t>
   </si>
   <si>
+    <t xml:space="preserve">DOTT (release)
+PE · Bell</t>
+  </si>
+  <si>
     <t>Lincoln Rose  ·  classroom teacher (LA9)</t>
   </si>
   <si>
@@ -2304,6 +2356,10 @@
 own class</t>
   </si>
   <si>
+    <t xml:space="preserve">DOTT (release)
+PE · Pevitt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leadership
 SSTUWA</t>
   </si>
@@ -2351,18 +2407,18 @@
 own class</t>
   </si>
   <si>
+    <t xml:space="preserve">Collaboration
+Y2 meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOTT (release)
+Health · Bell</t>
+  </si>
+  <si>
     <t xml:space="preserve">DOTT (release)
 Auslan · Peak</t>
   </si>
   <si>
-    <t xml:space="preserve">DOTT (release)
-Health · Bell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaboration
-Y2 meeting</t>
-  </si>
-  <si>
     <t>Savannah Espach  ·  classroom teacher (LA19)</t>
   </si>
   <si>
@@ -2399,10 +2455,6 @@
 Y1 meeting</t>
   </si>
   <si>
-    <t xml:space="preserve">DOTT (release)
-PE · Lowndes</t>
-  </si>
-  <si>
     <t>Ashlee Hutchings  ·  classroom teacher (LA23)</t>
   </si>
   <si>
@@ -2410,25 +2462,17 @@
 own class</t>
   </si>
   <si>
+    <t>Chloe Moore  ·  classroom teacher (LA24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24
+own class</t>
+  </si>
+  <si>
     <t xml:space="preserve">DOTT (release)
 Health · Lowndes</t>
   </si>
   <si>
-    <t xml:space="preserve">DOTT (release)
-PE · Bell</t>
-  </si>
-  <si>
-    <t>Chloe Moore  ·  classroom teacher (LA24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24
-own class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOTT (release)
-PE · Pevitt</t>
-  </si>
-  <si>
     <t>Chantel Uhe  ·  specialist (0.4 teach; works Tue/Wed)</t>
   </si>
   <si>
@@ -2469,23 +2513,67 @@
     <t>Lis Lowndes  ·  specialist (1.0; works Mon/Tue/Wed/Thu/Fri)</t>
   </si>
   <si>
+    <t xml:space="preserve">LA18 (2)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration
+STEM/PE team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24 (1)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+STEM</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA20 (2)
 STEM</t>
   </si>
   <si>
+    <t xml:space="preserve">LA7 (5)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA18 (2)
+PE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA24 (1)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaboration
-STEM/PE team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA6 (5/6)
+Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
 PE</t>
   </si>
   <si>
@@ -2493,39 +2581,243 @@
 (Luca)</t>
   </si>
   <si>
+    <t>Natalie Carter  ·  specialist (0.6; works Mon/Tue/Wed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leadership
+PBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24 (1)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA17 (4/5)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+Visual Art</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA15 (3)
-STEM</t>
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA7 (5)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA18 (2)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA16 (4)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA20 (2)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+Visual Art</t>
   </si>
   <si>
     <t xml:space="preserve">LA23 (1)
-STEM</t>
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration
+Arts team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA8 (6)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA9 (5/6)
+Visual Art</t>
+  </si>
+  <si>
+    <t>Cheryl Peak  ·  specialist (0.8; works Tue/Wed/Thu/Fri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA20 (2)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24 (1)
+Performing Arts</t>
   </si>
   <si>
     <t xml:space="preserve">LA7 (5)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA8 (6)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA16 (4)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA9 (5/6)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leadership
+Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA18 (2)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA17 (4/5)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA18 (2)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA20 (2)
+Auslan</t>
+  </si>
+  <si>
+    <t>Rachel Walker  ·  specialist (0.4; works Wed/Thu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA8 (6)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA7 (5)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA9 (5/6)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24 (1)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA17 (4/5)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA16 (4)
+Auslan</t>
+  </si>
+  <si>
+    <t>Aaron Bell  ·  specialist (0.4; works Thu/Fri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA8 (6)
 PE</t>
   </si>
   <si>
+    <t xml:space="preserve">LA9 (5/6)
+Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA16 (4)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA18 (2)
+Health</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA19 (2)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
 PE</t>
   </si>
   <si>
-    <t xml:space="preserve">LA21 (3)
-STEM</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA22 (1)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
+Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
 PE</t>
   </si>
   <si>
@@ -2533,254 +2825,6 @@
 Health</t>
   </si>
   <si>
-    <t xml:space="preserve">LA22 (1)
-PE</t>
-  </si>
-  <si>
-    <t>Natalie Carter  ·  specialist (0.6; works Mon/Tue/Wed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA6 (5/6)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA19 (2)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaboration
-Arts team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leadership
-PBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7 (5)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24 (1)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA16 (4)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA8 (6)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA17 (4/5)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA20 (2)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA9 (5/6)
-Visual Art</t>
-  </si>
-  <si>
-    <t>Cheryl Peak  ·  specialist (0.8; works Tue/Wed/Thu/Fri)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leadership
-Events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA9 (5/6)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA20 (2)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA16 (4)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA6 (5/6)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA20 (2)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA17 (4/5)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA19 (2)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7 (5)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24 (1)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA8 (6)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA19 (2)
-Auslan</t>
-  </si>
-  <si>
-    <t>Rachel Walker  ·  specialist (0.4; works Wed/Thu)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA6 (5/6)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA8 (6)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24 (1)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA17 (4/5)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA9 (5/6)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7 (5)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA16 (4)
-Auslan</t>
-  </si>
-  <si>
-    <t>Aaron Bell  ·  specialist (0.4; works Thu/Fri)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA8 (6)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA16 (4)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA19 (2)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA9 (5/6)
-Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24 (1)
-Health</t>
-  </si>
-  <si>
     <t>Jake Pevitt  ·  specialist (0.2 (Thu); works Thu)</t>
   </si>
   <si>
@@ -2963,7 +3007,7 @@
     <t>| Y1 | Wed P4 | LA22: Imogen Webb (Visual Art/Carter); LA23: Ashlee Hutchings (Performing Arts/Peak); LA24: Chloe Moore (Auslan/Walker) | PASS |</t>
   </si>
   <si>
-    <t>| Y2 | Thu P5 | LA18: Hannah Bouwmeester (PE/Lowndes); LA19: Savannah Espach (PE/Bell); LA20: Anna Hendron (PE/Pevitt) | PASS |</t>
+    <t>| Y2 | Wed P3 | LA18: Hannah Bouwmeester (Visual Art/Carter); LA19: Savannah Espach (Performing Arts/Peak); LA20: Anna Hendron (STEM/Lowndes) | PASS |</t>
   </si>
   <si>
     <t>| Y3-4 | Thu P4 | LA14: Olivia Sheehy (PE/Lowndes); LA15: Georgia Mitchell (PE/Bell); LA21: Jasper Sirr-Davis (PE/Pevitt) | PASS |</t>
@@ -2972,10 +3016,10 @@
     <t>| Y4-5 | Thu P3 | LA7: Nicola Pigott (PE/Lowndes); LA16: Tanya Thieme (PE/Bell); LA17: Cassidy Law (PE/Pevitt) | PASS |</t>
   </si>
   <si>
-    <t>| Y5-6 | Thu P2 | LA6: John Dunbar (PE/Lowndes); LA8: Janette Crisp (PE/Bell); LA9: Lincoln Rose (PE/Pevitt) | PASS |</t>
-  </si>
-  <si>
-    <t>| Arts | Wed P2 | Peak, Carter, Walker all on DOTT | PASS |</t>
+    <t>| Y5-6 | Wed P2 | LA6: John Dunbar (Visual Art/Carter); LA8: Janette Crisp (Performing Arts/Peak); LA9: Lincoln Rose (Auslan/Walker) | PASS |</t>
+  </si>
+  <si>
+    <t>| Arts | Wed P5 | Peak, Carter, Walker all on DOTT | PASS |</t>
   </si>
   <si>
     <t>| STEM/PE | Thu P1 | Bell, Lowndes on DOTT; Uhe joins from Thursday office | PASS |</t>
@@ -2993,31 +3037,31 @@
     <t>| --- | --- | --- | --- | --- |</t>
   </si>
   <si>
-    <t>| Mon | LA17 | Visual Art | Natalie Carter | base release |</t>
-  </si>
-  <si>
-    <t>| Mon | LA22 | STEM | Lis Lowndes | base release |</t>
-  </si>
-  <si>
-    <t>| Tue | LA14 | Performing Arts | Cheryl Peak | base release |</t>
-  </si>
-  <si>
-    <t>| Tue | LA18 | STEM | Lis Lowndes | base release |</t>
-  </si>
-  <si>
-    <t>| Tue | LA20 | Visual Art | Natalie Carter | base release |</t>
+    <t>| Mon | LA24 | Health | Lis Lowndes | grad extra |</t>
+  </si>
+  <si>
+    <t>| Mon | LA8 | Visual Art | Natalie Carter | base release |</t>
+  </si>
+  <si>
+    <t>| Tue | LA17 | Performing Arts | Cheryl Peak | base release |</t>
+  </si>
+  <si>
+    <t>| Tue | LA19 | Visual Art | Natalie Carter | base release |</t>
+  </si>
+  <si>
+    <t>| Tue | LA22 | STEM | Lis Lowndes | base release |</t>
   </si>
   <si>
     <t>| Tue | LA6 | STEM | Chantel Uhe | base release |</t>
   </si>
   <si>
+    <t>| Wed | LA14 | Auslan | Rachel Walker | base release |</t>
+  </si>
+  <si>
     <t>| Wed | LA15 | Performing Arts | Cheryl Peak | base release |</t>
   </si>
   <si>
-    <t>| Wed | LA21 | Auslan | Rachel Walker | base release |</t>
-  </si>
-  <si>
-    <t>| Wed | LA23 | Health | Lis Lowndes | grad extra |</t>
+    <t>| Wed | LA21 | STEM | Lis Lowndes | base release |</t>
   </si>
   <si>
     <t>| Wed | LA7 | STEM | Chantel Uhe | base release |</t>
@@ -3029,6 +3073,9 @@
     <t>| Thu | LA16 | Auslan | Rachel Walker | base release |</t>
   </si>
   <si>
+    <t>| Thu | LA18 | Performing Arts | Cheryl Peak | base release |</t>
+  </si>
+  <si>
     <t>| Thu | LA22 | PE | Lis Lowndes | base release |</t>
   </si>
   <si>
@@ -3038,13 +3085,10 @@
     <t>| Thu | LA24 | PE | Jake Pevitt | base release |</t>
   </si>
   <si>
-    <t>| Thu | LA8 | Performing Arts | Cheryl Peak | base release |</t>
-  </si>
-  <si>
-    <t>| Fri | LA19 | Auslan | Cheryl Peak | base release |</t>
-  </si>
-  <si>
-    <t>| Fri | LA24 | Health | Aaron Bell | grad extra |</t>
+    <t>| Fri | LA20 | Auslan | Cheryl Peak | base release |</t>
+  </si>
+  <si>
+    <t>| Fri | LA23 | Health | Aaron Bell | grad extra |</t>
   </si>
   <si>
     <t>Every class has a Period 6 release: PASS. (15 base releases; 2 grad Health remain in P6, the others moved to Friday by design.)</t>
@@ -3056,16 +3100,16 @@
     <t>| Teacher | Role | Slot | Detail |</t>
   </si>
   <si>
-    <t>| Natalie Carter | PBS | Mon P3 | fixed |</t>
-  </si>
-  <si>
-    <t>| Cheryl Peak | Events | Tue P1 | Peak non-teaching block |</t>
-  </si>
-  <si>
-    <t>| Jasper Sirr-Davis | OHS | Fri P2 | LA21 covered by Aaron Bell (Health) · additional 45-min release on top of normal DOTT |</t>
-  </si>
-  <si>
-    <t>| Lincoln Rose | SSTUWA | Fri P5 | LA9 covered by Aaron Bell (Health) · additional 45-min release on top of normal DOTT |</t>
+    <t>| Natalie Carter | PBS | Mon P1 | fixed (moved from Mon P3 so LA23 can take P3 - Brad item 5) |</t>
+  </si>
+  <si>
+    <t>| Cheryl Peak | Events | Tue P5 | Peak non-teaching block |</t>
+  </si>
+  <si>
+    <t>| Lincoln Rose | SSTUWA | Fri P2 | LA9 covered by Aaron Bell (Health) · additional 45-min release on top of normal DOTT |</t>
+  </si>
+  <si>
+    <t>| Jasper Sirr-Davis | OHS | Fri P3 | LA21 covered by Aaron Bell (Health) · additional 45-min release on top of normal DOTT |</t>
   </si>
   <si>
     <t>All four leadership blocks placed: PASS. Each is a genuine extra 45-min release on top of the teacher's normal DOTT. Carter (PBS) and Peak (Events) are specialists, so their block is a non-teaching period in their own timetable. Rose (SSTUWA) and Sirr-Davis (OHS) are classroom teachers, so Aaron Bell teaches their class a Health period to release them (Friday). This is why LA9 and LA21 carry a third specialist period on that day (a deliberate exception to the 2-per-day rule for the leadership release).</t>
@@ -3074,7 +3118,7 @@
     <t>4. Monday P0 and P1 vacancy</t>
   </si>
   <si>
-    <t>Monday P0 specialist lessons: 0. Monday P1 specialist lessons: 2. Clear of all specialist activity: FAIL.</t>
+    <t>Monday P0 specialist lessons: 0. Monday P1 specialist lessons: 0. Clear of all specialist activity: PASS.</t>
   </si>
   <si>
     <t>5. DOTT equity</t>
@@ -3263,49 +3307,49 @@
     <t>| --- | --- | --- | --- | --- | --- | --- |</t>
   </si>
   <si>
-    <t>| LA6 | 1 | 2 | 1 | 2 | 0 | 2 |</t>
+    <t>| LA6 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA7 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
-    <t>| LA8 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
+    <t>| LA8 | 1 | 2 | 2 | 1 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA9 | 0 | 2 | 2 | 2 | 1 | 2 |</t>
   </si>
   <si>
-    <t>| LA14 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA15 | 2 | 0 | 2 | 2 | 0 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA16 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA17 | 1 | 1 | 2 | 2 | 0 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA18 | 1 | 2 | 1 | 1 | 2 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA19 | 0 | 1 | 2 | 2 | 1 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA20 | 2 | 2 | 0 | 1 | 1 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA21 | 0 | 0 | 2 | 2 | 3 | 3 (incl leadership) |</t>
-  </si>
-  <si>
-    <t>| LA22 | 2 | 0 | 1 | 2 | 2 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA23 | 1 | 2 | 2 | 1 | 1 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA24 | 1 | 2 | 1 | 2 | 1 | 2 |</t>
+    <t>| LA14 | 1 | 2 | 1 | 2 | 0 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA15 | 1 | 0 | 1 | 2 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA16 | 1 | 1 | 2 | 2 | 0 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA17 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA18 | 0 | 2 | 1 | 2 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA19 | 2 | 1 | 1 | 1 | 1 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA20 | 0 | 2 | 2 | 1 | 1 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA21 | 1 | 1 | 2 | 2 | 1 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA22 | 0 | 2 | 1 | 2 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA23 | 2 | 1 | 1 | 1 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA24 | 1 | 1 | 1 | 2 | 2 | 2 |</t>
   </si>
   <si>
     <t>Within the daily cap (2 per class, 3 for the two leadership classes on their leadership day): PASS.</t>
@@ -3341,7 +3385,7 @@
     <t>STEM (rule 5): every STEM block is two back-to-back periods (consecutive period numbers, same day): PASS.</t>
   </si>
   <si>
-    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:8  P2:15  P3:17  P4:19  P5:19  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
+    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:9  P2:17  P3:18  P4:19  P5:15  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
   </si>
   <si>
     <t>10. Pre-Primary &amp; Kindy DOTT ledger</t>
@@ -3362,7 +3406,7 @@
     <t>| Katie Digney | PP | LA1 | 0.8 | 256m | 265m | +9m |</t>
   </si>
   <si>
-    <t>| Nikki Luca | PP | LA1 | 0.4 | 128m | 135m | +7m |</t>
+    <t>| Nikki Luca | PP | LA1 | 0.4 | 128m | 105m | -23m |</t>
   </si>
   <si>
     <t>| Kelly Duggan | Kindy | LA4 | 0.8 | 256m | 260m | +4m |</t>
@@ -4007,7 +4051,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" ht="72" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -4025,7 +4069,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" ht="88" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" ht="72" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -4324,8 +4368,8 @@
       <c r="K4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L4" s="10" t="s">
-        <v>81</v>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M4" s="9" t="s">
         <v>76</v>
@@ -4333,8 +4377,8 @@
       <c r="N4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>82</v>
+      <c r="O4" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P4" s="9" t="s">
         <v>79</v>
@@ -4342,10 +4386,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>66</v>
@@ -4371,14 +4415,14 @@
       <c r="J5" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>76</v>
+      <c r="K5" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>77</v>
@@ -4409,8 +4453,8 @@
       <c r="F6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>81</v>
+      <c r="G6" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>71</v>
@@ -4421,8 +4465,8 @@
       <c r="J6" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>74</v>
+      <c r="K6" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>75</v>
@@ -4481,17 +4525,17 @@
       <c r="F8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>71</v>
+      <c r="G8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="11" t="s">
-        <v>82</v>
+      <c r="J8" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>74</v>
@@ -4505,8 +4549,8 @@
       <c r="N8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="9" t="s">
-        <v>78</v>
+      <c r="O8" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="P8" s="9" t="s">
         <v>79</v>
@@ -4528,8 +4572,8 @@
       <c r="E9" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>69</v>
+      <c r="F9" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>70</v>
@@ -4552,14 +4596,14 @@
       <c r="M9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="P9" s="11" t="s">
+      <c r="N9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>82</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4594,8 +4638,8 @@
       <c r="C11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>67</v>
+      <c r="D11" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>68</v>
@@ -4609,8 +4653,8 @@
       <c r="H11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>82</v>
+      <c r="I11" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>73</v>
@@ -4624,19 +4668,19 @@
       <c r="M11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N11" s="10" t="s">
-        <v>81</v>
+      <c r="N11" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="9" t="s">
-        <v>79</v>
+      <c r="P11" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4765,7 +4809,7 @@
         <v>66</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>68</v>
@@ -4782,14 +4826,14 @@
       <c r="I16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>73</v>
+      <c r="J16" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>75</v>
+      <c r="L16" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>76</v>
@@ -4800,22 +4844,22 @@
       <c r="O16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P16" s="10" t="s">
-        <v>81</v>
+      <c r="P16" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>66</v>
+      <c r="C17" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>68</v>
@@ -4829,17 +4873,17 @@
       <c r="H17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K17" s="11" t="s">
+      <c r="I17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L17" s="13" t="s">
-        <v>92</v>
+      <c r="K17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>76</v>
@@ -4850,8 +4894,8 @@
       <c r="O17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>81</v>
+      <c r="P17" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4861,23 +4905,23 @@
       <c r="B18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>66</v>
+      <c r="C18" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>70</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>72</v>
@@ -4897,8 +4941,8 @@
       <c r="N18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O18" s="10" t="s">
-        <v>81</v>
+      <c r="O18" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P18" s="9" t="s">
         <v>79</v>
@@ -4933,17 +4977,17 @@
       <c r="B20" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>82</v>
+      <c r="C20" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>69</v>
+        <v>92</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>70</v>
@@ -4951,8 +4995,8 @@
       <c r="H20" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>92</v>
+      <c r="I20" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>73</v>
@@ -4960,17 +5004,17 @@
       <c r="K20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L20" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>76</v>
+      <c r="L20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O20" s="10" t="s">
-        <v>81</v>
+      <c r="O20" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P20" s="9" t="s">
         <v>79</v>
@@ -4981,10 +5025,10 @@
         <v>87</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="13" t="s">
         <v>92</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>67</v>
@@ -4998,14 +5042,14 @@
       <c r="G21" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>82</v>
+      <c r="H21" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J21" s="10" t="s">
-        <v>81</v>
+      <c r="J21" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>74</v>
@@ -5016,11 +5060,11 @@
       <c r="M21" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>78</v>
+      <c r="N21" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>79</v>
@@ -5053,7 +5097,7 @@
         <v>89</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>66</v>
@@ -5064,8 +5108,8 @@
       <c r="E23" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>92</v>
+      <c r="F23" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>70</v>
@@ -5073,23 +5117,23 @@
       <c r="H23" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>82</v>
+      <c r="I23" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M23" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N23" s="9" t="s">
-        <v>77</v>
+      <c r="N23" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>78</v>
@@ -5100,7 +5144,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -5222,14 +5266,14 @@
       <c r="A28" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>65</v>
+      <c r="B28" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>67</v>
+      <c r="D28" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>68</v>
@@ -5244,7 +5288,7 @@
         <v>71</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>73</v>
@@ -5255,8 +5299,8 @@
       <c r="L28" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="11" t="s">
-        <v>82</v>
+      <c r="M28" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>77</v>
@@ -5270,22 +5314,22 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>81</v>
+      <c r="D29" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>70</v>
@@ -5294,7 +5338,7 @@
         <v>71</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>73</v>
@@ -5322,38 +5366,38 @@
       <c r="A30" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>92</v>
+      <c r="B30" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>94</v>
+      <c r="D30" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>82</v>
+      <c r="F30" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>75</v>
+      <c r="J30" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="M30" s="9" t="s">
         <v>76</v>
@@ -5413,7 +5457,7 @@
         <v>70</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>72</v>
@@ -5421,23 +5465,23 @@
       <c r="J32" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K32" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>75</v>
+      <c r="K32" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="M32" s="9" t="s">
         <v>76</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -5448,13 +5492,13 @@
         <v>65</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>69</v>
@@ -5468,17 +5512,17 @@
       <c r="I33" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>81</v>
+      <c r="J33" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M33" s="9" t="s">
-        <v>76</v>
+      <c r="M33" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>77</v>
@@ -5520,19 +5564,19 @@
         <v>65</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>69</v>
+        <v>83</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>71</v>
@@ -5549,14 +5593,14 @@
       <c r="L35" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M35" s="14" t="s">
-        <v>94</v>
+      <c r="M35" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O35" s="10" t="s">
-        <v>95</v>
+      <c r="O35" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>79</v>
@@ -5686,17 +5730,17 @@
       <c r="A40" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>66</v>
+      <c r="B40" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>92</v>
+      <c r="E40" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>69</v>
@@ -5728,13 +5772,13 @@
       <c r="O40" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P40" s="9" t="s">
-        <v>79</v>
+      <c r="P40" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>97</v>
@@ -5748,11 +5792,11 @@
       <c r="E41" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F41" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>70</v>
+      <c r="F41" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>71</v>
@@ -5769,8 +5813,8 @@
       <c r="L41" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M41" s="13" t="s">
-        <v>92</v>
+      <c r="M41" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>77</v>
@@ -5798,11 +5842,11 @@
       <c r="E42" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F42" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>94</v>
+      <c r="F42" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>98</v>
@@ -5819,11 +5863,11 @@
       <c r="L42" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M42" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="N42" s="13" t="s">
-        <v>92</v>
+      <c r="M42" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="O42" s="9" t="s">
         <v>78</v>
@@ -5858,8 +5902,8 @@
       <c r="A44" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>65</v>
+      <c r="B44" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>66</v>
@@ -5867,8 +5911,8 @@
       <c r="D44" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>68</v>
+      <c r="E44" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>97</v>
@@ -5879,14 +5923,14 @@
       <c r="H44" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I44" s="14" t="s">
-        <v>94</v>
+      <c r="I44" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K44" s="13" t="s">
-        <v>92</v>
+      <c r="K44" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>75</v>
@@ -5911,8 +5955,8 @@
       <c r="B45" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>94</v>
+      <c r="C45" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>67</v>
@@ -5929,8 +5973,8 @@
       <c r="H45" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I45" s="9" t="s">
-        <v>72</v>
+      <c r="I45" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="J45" s="10" t="s">
         <v>97</v>
@@ -5944,14 +5988,14 @@
       <c r="M45" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N45" s="9" t="s">
-        <v>77</v>
+      <c r="N45" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P45" s="13" t="s">
-        <v>92</v>
+      <c r="P45" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -5986,8 +6030,8 @@
       <c r="C47" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>92</v>
+      <c r="D47" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>68</v>
@@ -5999,13 +6043,13 @@
         <v>70</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J47" s="9" t="s">
-        <v>73</v>
+      <c r="J47" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>74</v>
@@ -6198,7 +6242,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>65</v>
@@ -6209,8 +6253,8 @@
       <c r="D53" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>68</v>
+      <c r="E53" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>69</v>
@@ -6224,8 +6268,8 @@
       <c r="I53" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J53" s="13" t="s">
-        <v>101</v>
+      <c r="J53" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>74</v>
@@ -6233,17 +6277,17 @@
       <c r="L53" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M53" s="15" t="s">
+      <c r="M53" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="N53" s="13" t="s">
         <v>102</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P53" s="9" t="s">
-        <v>79</v>
+      <c r="P53" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -6274,26 +6318,26 @@
       <c r="I54" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J54" s="15" t="s">
-        <v>102</v>
+      <c r="J54" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L54" s="13" t="s">
+      <c r="L54" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M54" s="15" t="s">
         <v>101</v>
-      </c>
-      <c r="M54" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="N54" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O54" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="P54" s="9" t="s">
-        <v>79</v>
+      <c r="O54" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -6337,8 +6381,8 @@
       <c r="F56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G56" s="9" t="s">
-        <v>70</v>
+      <c r="G56" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>71</v>
@@ -6346,23 +6390,23 @@
       <c r="I56" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J56" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>74</v>
+      <c r="J56" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="K56" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="L56" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M56" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N56" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="O56" s="13" t="s">
-        <v>101</v>
+      <c r="M56" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="O56" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P56" s="9" t="s">
         <v>79</v>
@@ -6381,14 +6425,14 @@
       <c r="D57" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E57" s="15" t="s">
-        <v>102</v>
+      <c r="E57" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>70</v>
+      <c r="G57" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>71</v>
@@ -6396,8 +6440,8 @@
       <c r="I57" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J57" s="9" t="s">
-        <v>73</v>
+      <c r="J57" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>74</v>
@@ -6405,10 +6449,10 @@
       <c r="L57" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M57" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N57" s="13" t="s">
+      <c r="M57" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="N57" s="15" t="s">
         <v>101</v>
       </c>
       <c r="O57" s="9" t="s">
@@ -6471,11 +6515,11 @@
       <c r="J59" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K59" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>75</v>
+      <c r="K59" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="M59" s="9" t="s">
         <v>76</v>
@@ -6483,11 +6527,11 @@
       <c r="N59" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O59" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="P59" s="15" t="s">
-        <v>102</v>
+      <c r="O59" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="P59" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -6582,11 +6626,11 @@
       <c r="C4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>65</v>
@@ -6594,16 +6638,16 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>65</v>
+      <c r="D5" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>97</v>
@@ -6622,8 +6666,8 @@
       <c r="C6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>92</v>
+      <c r="D6" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>65</v>
@@ -6657,8 +6701,8 @@
       <c r="D8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>65</v>
+      <c r="E8" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>65</v>
@@ -6672,7 +6716,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>65</v>
@@ -6704,7 +6748,7 @@
         <v>65</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>65</v>
@@ -6779,8 +6823,8 @@
       <c r="D16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>66</v>
+      <c r="E16" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>66</v>
@@ -6788,13 +6832,13 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>66</v>
+      <c r="C17" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>66</v>
@@ -6813,8 +6857,8 @@
       <c r="B18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>66</v>
+      <c r="C18" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>66</v>
@@ -6845,8 +6889,8 @@
       <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>82</v>
+      <c r="C20" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>66</v>
@@ -6865,14 +6909,14 @@
       <c r="B21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>94</v>
+      <c r="E21" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>66</v>
@@ -6901,7 +6945,7 @@
         <v>66</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>66</v>
@@ -6968,10 +7012,10 @@
         <v>67</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>67</v>
+        <v>92</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>67</v>
@@ -6982,16 +7026,16 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>67</v>
+        <v>92</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>98</v>
@@ -7010,8 +7054,8 @@
       <c r="C30" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>94</v>
+      <c r="D30" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>67</v>
@@ -7062,8 +7106,8 @@
       <c r="C33" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>82</v>
+      <c r="D33" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>67</v>
@@ -7088,8 +7132,8 @@
       <c r="A35" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>67</v>
+      <c r="B35" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>67</v>
@@ -7097,8 +7141,8 @@
       <c r="D35" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>92</v>
+      <c r="E35" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>67</v>
@@ -7167,8 +7211,8 @@
       <c r="D40" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>92</v>
+      <c r="E40" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>68</v>
@@ -7176,7 +7220,7 @@
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>68</v>
@@ -7184,14 +7228,14 @@
       <c r="C41" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>68</v>
+      <c r="D41" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>68</v>
+      <c r="F41" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7202,7 +7246,7 @@
         <v>68</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>68</v>
@@ -7234,13 +7278,13 @@
         <v>68</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>68</v>
+      <c r="E44" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
@@ -7256,14 +7300,14 @@
       <c r="C45" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="14" t="s">
-        <v>94</v>
+      <c r="D45" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="15" t="s">
-        <v>102</v>
+      <c r="F45" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7289,7 +7333,7 @@
         <v>68</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>68</v>
@@ -7370,7 +7414,7 @@
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>69</v>
@@ -7378,11 +7422,11 @@
       <c r="C53" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>94</v>
+      <c r="D53" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>69</v>
@@ -7395,14 +7439,14 @@
       <c r="B54" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" s="9" t="s">
+      <c r="D54" s="9" t="s">
         <v>69</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>69</v>
@@ -7427,8 +7471,8 @@
       <c r="B56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>69</v>
+      <c r="C56" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>69</v>
@@ -7444,8 +7488,8 @@
       <c r="A57" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>69</v>
+      <c r="B57" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>69</v>
@@ -7479,11 +7523,11 @@
       <c r="B59" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59" s="9" t="s">
+      <c r="C59" s="9" t="s">
         <v>69</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>69</v>
@@ -7564,7 +7608,7 @@
     </row>
     <row r="65" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>70</v>
@@ -7575,8 +7619,8 @@
       <c r="D65" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E65" s="9" t="s">
-        <v>70</v>
+      <c r="E65" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>70</v>
@@ -7586,17 +7630,17 @@
       <c r="A66" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>81</v>
+      <c r="B66" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>94</v>
+      <c r="D66" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>70</v>
@@ -7618,8 +7662,8 @@
       <c r="A68" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>81</v>
+      <c r="B68" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>70</v>
@@ -7630,8 +7674,8 @@
       <c r="E68" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F68" s="9" t="s">
-        <v>70</v>
+      <c r="F68" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7650,8 +7694,8 @@
       <c r="E69" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>70</v>
+      <c r="F69" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7677,7 +7721,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>70</v>
@@ -7758,7 +7802,7 @@
     </row>
     <row r="77" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>71</v>
@@ -7784,10 +7828,10 @@
         <v>71</v>
       </c>
       <c r="C78" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="E78" s="15" t="s">
         <v>98</v>
@@ -7812,14 +7856,14 @@
       <c r="A80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>71</v>
+      <c r="B80" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>71</v>
@@ -7835,8 +7879,8 @@
       <c r="B81" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C81" s="11" t="s">
-        <v>82</v>
+      <c r="C81" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>71</v>
@@ -7874,7 +7918,7 @@
         <v>71</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>71</v>
@@ -7941,7 +7985,7 @@
         <v>72</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>72</v>
@@ -7952,16 +7996,16 @@
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C89" s="9" t="s">
-        <v>72</v>
+      <c r="C89" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>72</v>
@@ -8009,14 +8053,14 @@
       <c r="B92" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>92</v>
+      <c r="C92" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E92" s="14" t="s">
-        <v>94</v>
+      <c r="E92" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>72</v>
@@ -8035,8 +8079,8 @@
       <c r="D93" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E93" s="9" t="s">
-        <v>72</v>
+      <c r="E93" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>72</v>
@@ -8058,11 +8102,11 @@
       <c r="A95" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C95" s="9" t="s">
+      <c r="B95" s="9" t="s">
         <v>72</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>72</v>
@@ -8131,8 +8175,8 @@
       <c r="B100" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C100" s="9" t="s">
-        <v>73</v>
+      <c r="C100" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>73</v>
@@ -8146,13 +8190,13 @@
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C101" s="9" t="s">
-        <v>73</v>
+      <c r="C101" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>73</v>
@@ -8160,8 +8204,8 @@
       <c r="E101" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F101" s="13" t="s">
-        <v>101</v>
+      <c r="F101" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="102" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8174,14 +8218,14 @@
       <c r="C102" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D102" s="9" t="s">
-        <v>73</v>
+      <c r="D102" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F102" s="15" t="s">
-        <v>102</v>
+      <c r="F102" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="103" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8200,8 +8244,8 @@
       <c r="A104" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B104" s="11" t="s">
-        <v>82</v>
+      <c r="B104" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>73</v>
@@ -8212,8 +8256,8 @@
       <c r="E104" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F104" s="9" t="s">
-        <v>73</v>
+      <c r="F104" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8223,17 +8267,17 @@
       <c r="B105" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>92</v>
+      <c r="C105" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F105" s="9" t="s">
-        <v>73</v>
+      <c r="F105" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8255,14 +8299,14 @@
       <c r="B107" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>81</v>
+      <c r="C107" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E107" s="9" t="s">
-        <v>73</v>
+      <c r="E107" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>73</v>
@@ -8340,13 +8384,13 @@
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B113" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C113" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>74</v>
@@ -8362,14 +8406,14 @@
       <c r="A114" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B114" s="9" t="s">
-        <v>74</v>
+      <c r="B114" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>74</v>
+      <c r="D114" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>74</v>
@@ -8400,14 +8444,14 @@
       <c r="C116" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D116" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F116" s="9" t="s">
+      <c r="D116" s="9" t="s">
         <v>74</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F116" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="117" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8420,8 +8464,8 @@
       <c r="C117" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D117" s="10" t="s">
-        <v>81</v>
+      <c r="D117" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>98</v>
@@ -8449,8 +8493,8 @@
       <c r="B119" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C119" s="9" t="s">
-        <v>74</v>
+      <c r="C119" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>74</v>
@@ -8458,8 +8502,8 @@
       <c r="E119" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F119" s="13" t="s">
-        <v>101</v>
+      <c r="F119" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -8516,11 +8560,11 @@
       <c r="A124" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C124" s="9" t="s">
+      <c r="B124" s="9" t="s">
         <v>75</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>75</v>
@@ -8534,13 +8578,13 @@
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B125" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C125" s="13" t="s">
-        <v>92</v>
+      <c r="B125" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>75</v>
@@ -8562,14 +8606,14 @@
       <c r="C126" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>75</v>
+      <c r="D126" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F126" s="13" t="s">
-        <v>101</v>
+      <c r="F126" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="127" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8591,11 +8635,11 @@
       <c r="B128" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C128" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>75</v>
+      <c r="C128" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D128" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>75</v>
@@ -8643,8 +8687,8 @@
       <c r="B131" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C131" s="11" t="s">
-        <v>82</v>
+      <c r="C131" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>75</v>
@@ -8652,8 +8696,8 @@
       <c r="E131" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F131" s="9" t="s">
-        <v>75</v>
+      <c r="F131" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -8716,8 +8760,8 @@
       <c r="C136" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D136" s="11" t="s">
-        <v>82</v>
+      <c r="D136" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>76</v>
@@ -8728,10 +8772,10 @@
     </row>
     <row r="137" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B137" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="C137" s="9" t="s">
         <v>76</v>
@@ -8739,11 +8783,11 @@
       <c r="D137" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F137" s="15" t="s">
-        <v>102</v>
+      <c r="E137" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="138" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8759,11 +8803,11 @@
       <c r="D138" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E138" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F138" s="9" t="s">
-        <v>76</v>
+      <c r="E138" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F138" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="139" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8785,8 +8829,8 @@
       <c r="B140" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C140" s="9" t="s">
-        <v>76</v>
+      <c r="C140" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D140" s="9" t="s">
         <v>76</v>
@@ -8794,8 +8838,8 @@
       <c r="E140" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F140" s="10" t="s">
-        <v>81</v>
+      <c r="F140" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="141" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8808,14 +8852,14 @@
       <c r="C141" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D141" s="9" t="s">
-        <v>76</v>
+      <c r="D141" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F141" s="10" t="s">
-        <v>81</v>
+      <c r="F141" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8840,8 +8884,8 @@
       <c r="C143" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D143" s="14" t="s">
-        <v>94</v>
+      <c r="D143" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>76</v>
@@ -8922,7 +8966,7 @@
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B149" s="9" t="s">
         <v>77</v>
@@ -8936,8 +8980,8 @@
       <c r="E149" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F149" s="9" t="s">
-        <v>77</v>
+      <c r="F149" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="150" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8953,8 +8997,8 @@
       <c r="D150" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E150" s="13" t="s">
-        <v>92</v>
+      <c r="E150" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>77</v>
@@ -8983,32 +9027,32 @@
         <v>77</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F152" s="15" t="s">
-        <v>102</v>
+      <c r="F152" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="153" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C153" s="9" t="s">
+      <c r="B153" s="9" t="s">
         <v>77</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D153" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E153" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F153" s="13" t="s">
+      <c r="E153" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F153" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -9028,11 +9072,11 @@
       <c r="A155" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B155" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C155" s="9" t="s">
+      <c r="B155" s="9" t="s">
         <v>77</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D155" s="9" t="s">
         <v>77</v>
@@ -9098,8 +9142,8 @@
       <c r="A160" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B160" s="11" t="s">
-        <v>82</v>
+      <c r="B160" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="C160" s="9" t="s">
         <v>78</v>
@@ -9116,7 +9160,7 @@
     </row>
     <row r="161" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B161" s="9" t="s">
         <v>78</v>
@@ -9141,8 +9185,8 @@
       <c r="B162" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>81</v>
+      <c r="C162" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="D162" s="9" t="s">
         <v>78</v>
@@ -9150,8 +9194,8 @@
       <c r="E162" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F162" s="9" t="s">
-        <v>78</v>
+      <c r="F162" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="163" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9170,31 +9214,31 @@
       <c r="A164" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C164" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C164" s="10" t="s">
-        <v>81</v>
-      </c>
       <c r="D164" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F164" s="13" t="s">
-        <v>101</v>
+      <c r="F164" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="165" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B165" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C165" s="9" t="s">
-        <v>78</v>
+      <c r="B165" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D165" s="9" t="s">
         <v>78</v>
@@ -9228,14 +9272,14 @@
       <c r="C167" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D167" s="10" t="s">
-        <v>95</v>
+      <c r="D167" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="E167" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F167" s="9" t="s">
-        <v>78</v>
+      <c r="F167" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -9295,14 +9339,14 @@
       <c r="B172" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>81</v>
+      <c r="C172" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E172" s="9" t="s">
-        <v>79</v>
+      <c r="E172" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>79</v>
@@ -9310,13 +9354,13 @@
     </row>
     <row r="173" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C173" s="10" t="s">
-        <v>81</v>
+      <c r="C173" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>79</v>
@@ -9324,8 +9368,8 @@
       <c r="E173" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F173" s="9" t="s">
-        <v>79</v>
+      <c r="F173" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="174" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9344,8 +9388,8 @@
       <c r="E174" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F174" s="9" t="s">
-        <v>79</v>
+      <c r="F174" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9371,7 +9415,7 @@
         <v>79</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E176" s="9" t="s">
         <v>79</v>
@@ -9384,8 +9428,8 @@
       <c r="A177" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B177" s="11" t="s">
-        <v>82</v>
+      <c r="B177" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>79</v>
@@ -9393,8 +9437,8 @@
       <c r="D177" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E177" s="13" t="s">
-        <v>92</v>
+      <c r="E177" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>79</v>
@@ -9416,8 +9460,8 @@
       <c r="A179" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B179" s="9" t="s">
-        <v>79</v>
+      <c r="B179" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="C179" s="9" t="s">
         <v>79</v>
@@ -9428,8 +9472,8 @@
       <c r="E179" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F179" s="15" t="s">
-        <v>102</v>
+      <c r="F179" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -9554,11 +9598,11 @@
       <c r="C4" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>120</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>119</v>
@@ -9566,18 +9610,18 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>121</v>
+        <v>81</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="18" t="s">
+      <c r="D5" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>122</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -9594,8 +9638,8 @@
       <c r="C6" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>123</v>
+      <c r="D6" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>119</v>
@@ -9629,8 +9673,8 @@
       <c r="D8" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>119</v>
+      <c r="E8" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>119</v>
@@ -9751,8 +9795,8 @@
       <c r="D16" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>126</v>
+      <c r="E16" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>126</v>
@@ -9760,13 +9804,13 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>126</v>
+      <c r="C17" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>126</v>
@@ -9785,14 +9829,14 @@
       <c r="B18" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>126</v>
+      <c r="C18" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>126</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>126</v>
@@ -9817,8 +9861,8 @@
       <c r="B20" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>121</v>
+      <c r="C20" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>126</v>
@@ -9837,14 +9881,14 @@
       <c r="B21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>123</v>
+      <c r="C21" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>120</v>
+      <c r="E21" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>126</v>
@@ -9884,7 +9928,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -9917,19 +9961,19 @@
         <v>64</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9937,39 +9981,39 @@
         <v>80</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>129</v>
+      <c r="D28" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>122</v>
+      <c r="D29" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>131</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9977,19 +10021,19 @@
         <v>84</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>120</v>
+        <v>130</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10009,19 +10053,19 @@
         <v>86</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10029,19 +10073,19 @@
         <v>87</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>121</v>
+        <v>130</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10060,25 +10104,25 @@
       <c r="A35" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>129</v>
+      <c r="B35" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>123</v>
+        <v>130</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -10111,19 +10155,19 @@
         <v>64</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10131,39 +10175,39 @@
         <v>80</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>123</v>
+        <v>133</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10171,19 +10215,19 @@
         <v>84</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>124</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10203,19 +10247,19 @@
         <v>86</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>124</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10223,19 +10267,19 @@
         <v>87</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>120</v>
+        <v>133</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10255,24 +10299,24 @@
         <v>89</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -10305,19 +10349,19 @@
         <v>64</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10325,39 +10369,39 @@
         <v>80</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>120</v>
+        <v>137</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10365,19 +10409,19 @@
         <v>84</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10397,39 +10441,39 @@
         <v>86</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>134</v>
+      <c r="B57" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10449,24 +10493,24 @@
         <v>89</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C59" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="E59" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -10499,19 +10543,19 @@
         <v>64</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10519,39 +10563,39 @@
         <v>80</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10559,19 +10603,19 @@
         <v>84</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>120</v>
+        <v>141</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10590,19 +10634,19 @@
       <c r="A68" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="17" t="s">
-        <v>135</v>
+      <c r="B68" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F68" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F68" s="17" t="s">
         <v>138</v>
       </c>
     </row>
@@ -10611,18 +10655,18 @@
         <v>87</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F69" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="17" t="s">
         <v>138</v>
       </c>
     </row>
@@ -10643,24 +10687,24 @@
         <v>89</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -10693,19 +10737,19 @@
         <v>64</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10713,39 +10757,39 @@
         <v>80</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10753,19 +10797,19 @@
         <v>84</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D78" s="17" t="s">
         <v>124</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10784,20 +10828,20 @@
       <c r="A80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>140</v>
+      <c r="B80" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D80" s="17" t="s">
         <v>124</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10805,19 +10849,19 @@
         <v>87</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C81" s="17" t="s">
-        <v>121</v>
+        <v>143</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10837,24 +10881,24 @@
         <v>89</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -10887,19 +10931,19 @@
         <v>64</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10907,39 +10951,39 @@
         <v>80</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D88" s="17" t="s">
         <v>124</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="D89" s="17" t="s">
         <v>124</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10947,19 +10991,19 @@
         <v>84</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10979,19 +11023,19 @@
         <v>86</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C92" s="17" t="s">
-        <v>123</v>
+        <v>145</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E92" s="17" t="s">
-        <v>120</v>
+        <v>145</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10999,19 +11043,19 @@
         <v>87</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11030,25 +11074,25 @@
       <c r="A95" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>142</v>
+      <c r="B95" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -11081,19 +11125,19 @@
         <v>64</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11101,39 +11145,39 @@
         <v>80</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F101" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="102" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11141,19 +11185,19 @@
         <v>84</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F102" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="103" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11172,20 +11216,20 @@
       <c r="A104" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B104" s="17" t="s">
-        <v>121</v>
+      <c r="B104" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="F104" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11193,19 +11237,19 @@
         <v>87</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C105" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D105" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E105" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F105" s="9" t="s">
-        <v>144</v>
+      <c r="C105" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F105" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11225,24 +11269,24 @@
         <v>89</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C107" s="17" t="s">
-        <v>135</v>
+        <v>147</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E107" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="E107" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -11275,19 +11319,19 @@
         <v>64</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11295,59 +11339,59 @@
         <v>80</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C113" s="17" t="s">
-        <v>121</v>
+        <v>81</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F113" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B114" s="9" t="s">
-        <v>149</v>
+      <c r="B114" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="115" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11367,19 +11411,19 @@
         <v>86</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D116" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E116" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F116" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="117" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11387,19 +11431,19 @@
         <v>87</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D117" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E117" s="17" t="s">
+        <v>131</v>
       </c>
       <c r="F117" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="118" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11419,24 +11463,24 @@
         <v>89</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>145</v>
+        <v>152</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -11469,59 +11513,59 @@
         <v>64</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C124" s="9" t="s">
-        <v>151</v>
+      <c r="B124" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B125" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C125" s="17" t="s">
-        <v>123</v>
+        <v>81</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11529,19 +11573,19 @@
         <v>84</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F126" s="17" t="s">
-        <v>145</v>
+        <v>154</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="127" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11561,19 +11605,19 @@
         <v>86</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="C128" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11581,19 +11625,19 @@
         <v>87</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E129" s="18" t="s">
-        <v>147</v>
+        <v>154</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11613,24 +11657,24 @@
         <v>89</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C131" s="17" t="s">
-        <v>121</v>
+        <v>154</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F131" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="F131" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -11663,19 +11707,19 @@
         <v>64</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="136" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11683,39 +11727,39 @@
         <v>80</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>121</v>
+        <v>156</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>153</v>
+        <v>81</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E137" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F137" s="19" t="s">
-        <v>154</v>
+        <v>156</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="138" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11723,19 +11767,19 @@
         <v>84</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E138" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F138" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="E138" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F138" s="19" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="139" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11755,19 +11799,19 @@
         <v>86</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C140" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E140" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>135</v>
+        <v>139</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="141" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11775,19 +11819,19 @@
         <v>87</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D141" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F141" s="17" t="s">
-        <v>135</v>
+        <v>156</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11807,24 +11851,24 @@
         <v>89</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -11857,19 +11901,19 @@
         <v>64</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11877,39 +11921,39 @@
         <v>80</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F149" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="F149" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="150" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11917,19 +11961,19 @@
         <v>84</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E150" s="17" t="s">
-        <v>123</v>
+        <v>159</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11949,39 +11993,39 @@
         <v>86</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D152" s="18" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F152" s="17" t="s">
-        <v>146</v>
+        <v>159</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="153" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C153" s="9" t="s">
-        <v>156</v>
+      <c r="B153" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C153" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E153" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="E153" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F153" s="17" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="154" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12000,25 +12044,25 @@
       <c r="A155" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B155" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C155" s="9" t="s">
-        <v>156</v>
+      <c r="B155" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -12051,59 +12095,59 @@
         <v>64</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F159" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B160" s="17" t="s">
-        <v>121</v>
+      <c r="B160" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F160" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="161" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F161" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12111,19 +12155,19 @@
         <v>84</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C162" s="17" t="s">
-        <v>135</v>
+        <v>162</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="163" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12142,40 +12186,40 @@
       <c r="A164" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D164" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C164" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D164" s="18" t="s">
-        <v>157</v>
-      </c>
       <c r="E164" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F164" s="17" t="s">
-        <v>145</v>
+        <v>162</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="165" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B165" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C165" s="9" t="s">
-        <v>160</v>
+      <c r="B165" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F165" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="166" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12195,19 +12239,19 @@
         <v>89</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D167" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="E167" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>160</v>
+        <v>131</v>
+      </c>
+      <c r="F167" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -12268,13 +12312,13 @@
         <v>164</v>
       </c>
       <c r="C172" s="17" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E172" s="9" t="s">
-        <v>164</v>
+      <c r="E172" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>164</v>
@@ -12282,13 +12326,13 @@
     </row>
     <row r="173" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C173" s="17" t="s">
-        <v>135</v>
+      <c r="C173" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>164</v>
@@ -12296,8 +12340,8 @@
       <c r="E173" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F173" s="9" t="s">
-        <v>164</v>
+      <c r="F173" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="174" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12316,8 +12360,8 @@
       <c r="E174" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F174" s="9" t="s">
-        <v>164</v>
+      <c r="F174" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12343,7 +12387,7 @@
         <v>164</v>
       </c>
       <c r="D176" s="18" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E176" s="9" t="s">
         <v>164</v>
@@ -12356,8 +12400,8 @@
       <c r="A177" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B177" s="17" t="s">
-        <v>121</v>
+      <c r="B177" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>164</v>
@@ -12365,8 +12409,8 @@
       <c r="D177" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E177" s="17" t="s">
-        <v>123</v>
+      <c r="E177" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>164</v>
@@ -12388,8 +12432,8 @@
       <c r="A179" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B179" s="9" t="s">
-        <v>164</v>
+      <c r="B179" s="17" t="s">
+        <v>165</v>
       </c>
       <c r="C179" s="9" t="s">
         <v>164</v>
@@ -12398,10 +12442,10 @@
         <v>164</v>
       </c>
       <c r="E179" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="F179" s="17" t="s">
-        <v>146</v>
+        <v>134</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -12476,7 +12520,7 @@
     </row>
     <row r="185" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B185" s="20" t="s">
         <v>167</v>
@@ -12652,17 +12696,17 @@
       <c r="A196" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B196" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C196" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="C196" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="D196" s="21" t="s">
         <v>168</v>
       </c>
       <c r="E196" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F196" s="21" t="s">
         <v>168</v>
@@ -12670,22 +12714,22 @@
     </row>
     <row r="197" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B197" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C197" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C197" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D197" s="10" t="s">
+      <c r="D197" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E197" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E197" s="10" t="s">
+      <c r="F197" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="F197" s="22" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="198" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12693,19 +12737,19 @@
         <v>84</v>
       </c>
       <c r="B198" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D198" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="E198" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D198" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E198" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F198" s="22" t="s">
-        <v>182</v>
+      <c r="F198" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="199" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12725,19 +12769,19 @@
         <v>86</v>
       </c>
       <c r="B200" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D200" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C200" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D200" s="10" t="s">
+      <c r="E200" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="E200" s="10" t="s">
+      <c r="F200" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="F200" s="10" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="201" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12745,19 +12789,19 @@
         <v>87</v>
       </c>
       <c r="B201" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D201" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="E201" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D201" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E201" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="F201" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12777,19 +12821,19 @@
         <v>89</v>
       </c>
       <c r="B203" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D203" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D203" s="10" t="s">
+      <c r="E203" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E203" s="10" t="s">
+      <c r="F203" s="22" t="s">
         <v>193</v>
-      </c>
-      <c r="F203" s="21" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -12846,14 +12890,14 @@
       <c r="A208" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B208" s="11" t="s">
+      <c r="B208" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="C208" s="21" t="s">
+      <c r="C208" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D208" s="21" t="s">
         <v>168</v>
-      </c>
-      <c r="D208" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="E208" s="20" t="s">
         <v>169</v>
@@ -12864,7 +12908,7 @@
     </row>
     <row r="209" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>197</v>
@@ -12872,7 +12916,7 @@
       <c r="C209" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D209" s="18" t="s">
+      <c r="D209" s="11" t="s">
         <v>199</v>
       </c>
       <c r="E209" s="20" t="s">
@@ -12886,7 +12930,7 @@
       <c r="A210" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B210" s="19" t="s">
+      <c r="B210" s="11" t="s">
         <v>200</v>
       </c>
       <c r="C210" s="11" t="s">
@@ -12944,7 +12988,7 @@
       <c r="C213" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D213" s="11" t="s">
+      <c r="D213" s="18" t="s">
         <v>208</v>
       </c>
       <c r="E213" s="20" t="s">
@@ -13043,14 +13087,14 @@
       <c r="B220" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="C220" s="19" t="s">
+      <c r="C220" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="D220" s="21" t="s">
-        <v>168</v>
+      <c r="D220" s="13" t="s">
+        <v>214</v>
       </c>
       <c r="E220" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F220" s="21" t="s">
         <v>168</v>
@@ -13058,22 +13102,22 @@
     </row>
     <row r="221" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B221" s="20" t="s">
         <v>169</v>
       </c>
       <c r="C221" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D221" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E221" s="13" t="s">
         <v>216</v>
       </c>
+      <c r="D221" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E221" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="F221" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="222" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13084,16 +13128,16 @@
         <v>169</v>
       </c>
       <c r="C222" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D222" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E222" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F222" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="223" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13116,16 +13160,16 @@
         <v>169</v>
       </c>
       <c r="C224" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E224" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F224" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="225" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13135,11 +13179,11 @@
       <c r="B225" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="C225" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D225" s="13" t="s">
+      <c r="C225" s="19" t="s">
         <v>227</v>
+      </c>
+      <c r="D225" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="E225" s="13" t="s">
         <v>228</v>
@@ -13240,11 +13284,11 @@
       <c r="C232" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D232" s="21" t="s">
-        <v>168</v>
+      <c r="D232" s="14" t="s">
+        <v>235</v>
       </c>
       <c r="E232" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F232" s="20" t="s">
         <v>169</v>
@@ -13252,7 +13296,7 @@
     </row>
     <row r="233" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B233" s="20" t="s">
         <v>169</v>
@@ -13260,11 +13304,11 @@
       <c r="C233" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D233" s="18" t="s">
-        <v>199</v>
+      <c r="D233" s="14" t="s">
+        <v>237</v>
       </c>
       <c r="E233" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F233" s="20" t="s">
         <v>169</v>
@@ -13280,11 +13324,11 @@
       <c r="C234" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D234" s="14" t="s">
-        <v>237</v>
+      <c r="D234" s="21" t="s">
+        <v>168</v>
       </c>
       <c r="E234" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F234" s="20" t="s">
         <v>169</v>
@@ -13313,10 +13357,10 @@
         <v>169</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E236" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F236" s="20" t="s">
         <v>169</v>
@@ -13332,8 +13376,8 @@
       <c r="C237" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D237" s="14" t="s">
-        <v>241</v>
+      <c r="D237" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="E237" s="14" t="s">
         <v>242</v>
@@ -13438,7 +13482,7 @@
         <v>169</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F244" s="21" t="s">
         <v>168</v>
@@ -13446,7 +13490,7 @@
     </row>
     <row r="245" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B245" s="20" t="s">
         <v>169</v>
@@ -13640,7 +13684,7 @@
     </row>
     <row r="257" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B257" s="20" t="s">
         <v>169</v>
@@ -13927,7 +13971,7 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>264</v>
@@ -14121,7 +14165,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>266</v>
@@ -14315,7 +14359,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>268</v>
@@ -14509,7 +14553,7 @@
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>169</v>
@@ -14523,8 +14567,8 @@
       <c r="E43" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F43" s="21" t="s">
-        <v>168</v>
+      <c r="F43" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14543,8 +14587,8 @@
       <c r="E44" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>168</v>
+      <c r="F44" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14627,8 +14671,8 @@
       <c r="E49" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>268</v>
+      <c r="F49" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -14703,7 +14747,7 @@
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>271</v>
@@ -14897,7 +14941,7 @@
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
@@ -15091,7 +15135,7 @@
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>169</v>
@@ -15285,7 +15329,7 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>168</v>
@@ -15479,7 +15523,7 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>283</v>
@@ -15493,8 +15537,8 @@
       <c r="E103" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F103" s="22" t="s">
-        <v>285</v>
+      <c r="F103" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15513,8 +15557,8 @@
       <c r="E104" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F104" s="22" t="s">
-        <v>285</v>
+      <c r="F104" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15597,8 +15641,8 @@
       <c r="E109" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>284</v>
+      <c r="F109" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -15673,7 +15717,7 @@
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>287</v>
@@ -15867,7 +15911,7 @@
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>290</v>
@@ -16061,7 +16105,7 @@
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B139" s="20" t="s">
         <v>293</v>
@@ -16255,7 +16299,7 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>291</v>
@@ -16449,7 +16493,7 @@
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B163" s="20" t="s">
         <v>293</v>
@@ -16643,7 +16687,7 @@
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>288</v>
@@ -16910,7 +16954,7 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>264</v>
@@ -17104,7 +17148,7 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>266</v>
@@ -17298,7 +17342,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>268</v>
@@ -17492,7 +17536,7 @@
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>169</v>
@@ -17506,8 +17550,8 @@
       <c r="E43" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F43" s="21" t="s">
-        <v>168</v>
+      <c r="F43" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17526,8 +17570,8 @@
       <c r="E44" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>168</v>
+      <c r="F44" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17610,8 +17654,8 @@
       <c r="E49" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>268</v>
+      <c r="F49" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -17686,7 +17730,7 @@
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>271</v>
@@ -17880,7 +17924,7 @@
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>274</v>
@@ -18074,7 +18118,7 @@
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>169</v>
@@ -18268,7 +18312,7 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>168</v>
@@ -18462,7 +18506,7 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>283</v>
@@ -18476,8 +18520,8 @@
       <c r="E103" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F103" s="22" t="s">
-        <v>285</v>
+      <c r="F103" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18496,8 +18540,8 @@
       <c r="E104" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F104" s="22" t="s">
-        <v>285</v>
+      <c r="F104" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18580,8 +18624,8 @@
       <c r="E109" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>284</v>
+      <c r="F109" s="22" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -18656,7 +18700,7 @@
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>287</v>
@@ -18850,7 +18894,7 @@
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>290</v>
@@ -19044,7 +19088,7 @@
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B139" s="20" t="s">
         <v>293</v>
@@ -19238,7 +19282,7 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>291</v>
@@ -19432,7 +19476,7 @@
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B163" s="20" t="s">
         <v>293</v>
@@ -19626,7 +19670,7 @@
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>288</v>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -2976,7 +2976,7 @@
 (class)</t>
   </si>
   <si>
-    <t xml:space="preserve">teacher
+    <t xml:space="preserve">Relief teacher
 (class)</t>
   </si>
   <si>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -2521,6 +2521,10 @@
 STEM/PE team</t>
   </si>
   <si>
+    <t xml:space="preserve">Cover T9
+(Dyer)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA19 (2)
 STEM</t>
   </si>
@@ -2976,10 +2980,6 @@
 (class)</t>
   </si>
   <si>
-    <t xml:space="preserve">Relief teacher
-(class)</t>
-  </si>
-  <si>
     <t>T10  ·  Kindy (Donna Campbell)</t>
   </si>
   <si>
@@ -3415,13 +3415,13 @@
     <t>| Donna Campbell | Kindy | T10 | 0.8 | 256m | 245m | -11m |</t>
   </si>
   <si>
-    <t>| Fiona Dyer | Kindy | T9 | 0.6 | 192m | 215m | +23m |</t>
+    <t>| Fiona Dyer | Kindy | T9 | 0.6 | 192m | 200m | +8m |</t>
   </si>
   <si>
     <t>| Anita Currion | Kindy | LA3 | 0.8 | 256m | 270m | +14m |</t>
   </si>
   <si>
-    <t>Outstanding holes to assign: Nikki Luca needs one more DOTT period (and her 2nd working day confirmed); the small −6 to −11 min/wk residuals (Jenny, Caroline, Katie, Kelly, Donna) are tracked. Fiona is covered by Aaron Bell on a spare Friday period; Kelly/Donna/Anita are covered by Anita's free Monday.</t>
+    <t>Tracked residuals: Nikki Luca sits -23 min/wk (Fri P5 Katie + Fri P6 Lis Lowndes = 105 vs 128); Brad pays this back outside the timetable. The small -6 to -11 min/wk residuals (Jenny, Caroline, Donna) are tracked. Fiona's Friday DOTT (P1) and Nikki's (P6) are both covered by Lis Lowndes; Kelly/Donna/Anita are covered by Anita's free Monday. No relief periods required.</t>
   </si>
 </sst>
 </file>
@@ -12708,8 +12708,8 @@
       <c r="E196" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F196" s="21" t="s">
-        <v>168</v>
+      <c r="F196" s="22" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="197" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12717,7 +12717,7 @@
         <v>81</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C197" s="10" t="s">
         <v>177</v>
@@ -12726,10 +12726,10 @@
         <v>168</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="198" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12737,19 +12737,19 @@
         <v>84</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C198" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D198" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F198" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="D198" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E198" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="199" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12769,19 +12769,19 @@
         <v>86</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D200" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="201" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12789,19 +12789,19 @@
         <v>87</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C201" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F201" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="D201" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E201" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12821,24 +12821,24 @@
         <v>89</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D203" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F203" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -12891,10 +12891,10 @@
         <v>80</v>
       </c>
       <c r="B208" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D208" s="21" t="s">
         <v>168</v>
@@ -12911,13 +12911,13 @@
         <v>81</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E209" s="20" t="s">
         <v>169</v>
@@ -12931,13 +12931,13 @@
         <v>84</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E210" s="20" t="s">
         <v>169</v>
@@ -12963,13 +12963,13 @@
         <v>86</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E212" s="20" t="s">
         <v>169</v>
@@ -12983,13 +12983,13 @@
         <v>87</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D213" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E213" s="20" t="s">
         <v>169</v>
@@ -13015,13 +13015,13 @@
         <v>89</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E215" s="20" t="s">
         <v>169</v>
@@ -13032,7 +13032,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -13088,13 +13088,13 @@
         <v>169</v>
       </c>
       <c r="C220" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D220" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E220" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F220" s="21" t="s">
         <v>168</v>
@@ -13108,16 +13108,16 @@
         <v>169</v>
       </c>
       <c r="C221" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D221" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E221" s="21" t="s">
         <v>168</v>
       </c>
       <c r="F221" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13128,16 +13128,16 @@
         <v>169</v>
       </c>
       <c r="C222" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D222" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E222" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F222" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="223" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13160,16 +13160,16 @@
         <v>169</v>
       </c>
       <c r="C224" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E224" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F224" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="225" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13180,16 +13180,16 @@
         <v>169</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D225" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E225" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F225" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="226" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13212,21 +13212,21 @@
         <v>169</v>
       </c>
       <c r="C227" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D227" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E227" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F227" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -13285,10 +13285,10 @@
         <v>169</v>
       </c>
       <c r="D232" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E232" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F232" s="20" t="s">
         <v>169</v>
@@ -13305,10 +13305,10 @@
         <v>169</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E233" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F233" s="20" t="s">
         <v>169</v>
@@ -13328,7 +13328,7 @@
         <v>168</v>
       </c>
       <c r="E234" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F234" s="20" t="s">
         <v>169</v>
@@ -13357,10 +13357,10 @@
         <v>169</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E236" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F236" s="20" t="s">
         <v>169</v>
@@ -13377,10 +13377,10 @@
         <v>169</v>
       </c>
       <c r="D237" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E237" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F237" s="20" t="s">
         <v>169</v>
@@ -13409,10 +13409,10 @@
         <v>169</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E239" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F239" s="20" t="s">
         <v>169</v>
@@ -13420,7 +13420,7 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -13502,10 +13502,10 @@
         <v>169</v>
       </c>
       <c r="E245" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F245" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="246" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13522,10 +13522,10 @@
         <v>169</v>
       </c>
       <c r="E246" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="247" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13554,10 +13554,10 @@
         <v>169</v>
       </c>
       <c r="E248" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F248" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="249" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13574,10 +13574,10 @@
         <v>169</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F249" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="250" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13606,15 +13606,15 @@
         <v>169</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F251" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
@@ -13696,7 +13696,7 @@
         <v>169</v>
       </c>
       <c r="E257" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F257" s="20" t="s">
         <v>169</v>
@@ -13716,7 +13716,7 @@
         <v>169</v>
       </c>
       <c r="E258" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F258" s="20" t="s">
         <v>169</v>
@@ -13748,7 +13748,7 @@
         <v>169</v>
       </c>
       <c r="E260" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F260" s="20" t="s">
         <v>169</v>
@@ -13768,7 +13768,7 @@
         <v>169</v>
       </c>
       <c r="E261" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F261" s="20" t="s">
         <v>169</v>
@@ -13800,7 +13800,7 @@
         <v>169</v>
       </c>
       <c r="E263" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F263" s="20" t="s">
         <v>169</v>
@@ -13891,7 +13891,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -13901,7 +13901,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -13934,16 +13934,16 @@
         <v>64</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F5" s="21" t="s">
         <v>168</v>
@@ -13954,16 +13954,16 @@
         <v>80</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>168</v>
@@ -13974,16 +13974,16 @@
         <v>81</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>168</v>
@@ -13994,16 +13994,16 @@
         <v>84</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>168</v>
@@ -14026,16 +14026,16 @@
         <v>86</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>168</v>
@@ -14046,16 +14046,16 @@
         <v>87</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>168</v>
@@ -14078,16 +14078,16 @@
         <v>89</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>168</v>
@@ -14095,7 +14095,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -14128,16 +14128,16 @@
         <v>64</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>168</v>
@@ -14148,16 +14148,16 @@
         <v>80</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>168</v>
@@ -14168,16 +14168,16 @@
         <v>81</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>168</v>
@@ -14188,16 +14188,16 @@
         <v>84</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>168</v>
@@ -14220,16 +14220,16 @@
         <v>86</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>168</v>
@@ -14240,16 +14240,16 @@
         <v>87</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>168</v>
@@ -14272,16 +14272,16 @@
         <v>89</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>168</v>
@@ -14289,7 +14289,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -14322,13 +14322,13 @@
         <v>64</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>169</v>
@@ -14342,13 +14342,13 @@
         <v>80</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>169</v>
@@ -14362,13 +14362,13 @@
         <v>81</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>169</v>
@@ -14382,13 +14382,13 @@
         <v>84</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>169</v>
@@ -14414,13 +14414,13 @@
         <v>86</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E34" s="20" t="s">
         <v>169</v>
@@ -14434,19 +14434,19 @@
         <v>87</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14466,13 +14466,13 @@
         <v>89</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>169</v>
@@ -14483,7 +14483,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -14525,10 +14525,10 @@
         <v>169</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14545,10 +14545,10 @@
         <v>169</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14565,10 +14565,10 @@
         <v>169</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14585,10 +14585,10 @@
         <v>169</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14617,10 +14617,10 @@
         <v>169</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14637,7 +14637,7 @@
         <v>169</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F47" s="21" t="s">
         <v>168</v>
@@ -14669,7 +14669,7 @@
         <v>169</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F49" s="21" t="s">
         <v>168</v>
@@ -14677,7 +14677,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -14710,19 +14710,19 @@
         <v>64</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14730,19 +14730,19 @@
         <v>80</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E54" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14750,19 +14750,19 @@
         <v>81</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E55" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14770,19 +14770,19 @@
         <v>84</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E56" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14802,19 +14802,19 @@
         <v>86</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E58" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14825,16 +14825,16 @@
         <v>168</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E59" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14857,21 +14857,21 @@
         <v>168</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E61" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -14904,19 +14904,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E65" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14924,19 +14924,19 @@
         <v>80</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E66" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14944,19 +14944,19 @@
         <v>81</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E67" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14967,16 +14967,16 @@
         <v>168</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E68" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14999,16 +14999,16 @@
         <v>168</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E70" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15016,19 +15016,19 @@
         <v>87</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E71" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15048,24 +15048,24 @@
         <v>89</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E73" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -15104,13 +15104,13 @@
         <v>169</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15124,13 +15124,13 @@
         <v>169</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15144,13 +15144,13 @@
         <v>169</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15164,13 +15164,13 @@
         <v>169</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15196,13 +15196,13 @@
         <v>169</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15216,13 +15216,13 @@
         <v>169</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15248,18 +15248,18 @@
         <v>169</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F85" s="21" t="s">
-        <v>168</v>
+        <v>278</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -15298,13 +15298,13 @@
         <v>169</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15318,13 +15318,13 @@
         <v>169</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15338,13 +15338,13 @@
         <v>169</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15352,19 +15352,19 @@
         <v>84</v>
       </c>
       <c r="B92" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C92" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>279</v>
-      </c>
       <c r="E92" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15384,19 +15384,19 @@
         <v>86</v>
       </c>
       <c r="B94" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C94" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>279</v>
-      </c>
       <c r="E94" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15404,19 +15404,19 @@
         <v>87</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C95" s="20" t="s">
         <v>169</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15436,24 +15436,24 @@
         <v>89</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C97" s="20" t="s">
         <v>169</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -15486,19 +15486,19 @@
         <v>64</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15506,19 +15506,19 @@
         <v>80</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15526,19 +15526,19 @@
         <v>81</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15546,19 +15546,19 @@
         <v>84</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15578,19 +15578,19 @@
         <v>86</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15598,19 +15598,19 @@
         <v>87</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E107" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F107" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15630,24 +15630,24 @@
         <v>89</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F109" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -15680,19 +15680,19 @@
         <v>64</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15700,19 +15700,19 @@
         <v>80</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F114" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15720,19 +15720,19 @@
         <v>81</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F115" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="116" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15740,19 +15740,19 @@
         <v>84</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F116" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="117" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15772,19 +15772,19 @@
         <v>86</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F118" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="119" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15792,19 +15792,19 @@
         <v>87</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F119" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="120" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15824,24 +15824,24 @@
         <v>89</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F121" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -15874,19 +15874,19 @@
         <v>64</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="126" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15894,19 +15894,19 @@
         <v>80</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F126" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15914,19 +15914,19 @@
         <v>81</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="128" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15934,19 +15934,19 @@
         <v>84</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="129" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15966,19 +15966,19 @@
         <v>86</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F130" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="131" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15986,19 +15986,19 @@
         <v>87</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="132" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16018,24 +16018,24 @@
         <v>89</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -16068,19 +16068,19 @@
         <v>64</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="138" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16088,19 +16088,19 @@
         <v>80</v>
       </c>
       <c r="B138" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16108,19 +16108,19 @@
         <v>81</v>
       </c>
       <c r="B139" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="140" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16128,19 +16128,19 @@
         <v>84</v>
       </c>
       <c r="B140" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="141" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16160,19 +16160,19 @@
         <v>86</v>
       </c>
       <c r="B142" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16180,19 +16180,19 @@
         <v>87</v>
       </c>
       <c r="B143" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16212,24 +16212,24 @@
         <v>89</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -16262,19 +16262,19 @@
         <v>64</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="150" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16282,19 +16282,19 @@
         <v>80</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F150" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16302,19 +16302,19 @@
         <v>81</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E151" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16322,19 +16322,19 @@
         <v>84</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F152" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16354,19 +16354,19 @@
         <v>86</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E154" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F154" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16374,19 +16374,19 @@
         <v>87</v>
       </c>
       <c r="B155" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E155" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C155" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D155" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E155" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="F155" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16406,24 +16406,24 @@
         <v>89</v>
       </c>
       <c r="B157" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E157" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C157" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D157" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E157" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="F157" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -16456,19 +16456,19 @@
         <v>64</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C161" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F161" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="162" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16476,19 +16476,19 @@
         <v>80</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C162" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+      <c r="F162" s="22" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16496,19 +16496,19 @@
         <v>81</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C163" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F163" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="164" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16516,19 +16516,19 @@
         <v>84</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C164" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F164" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="165" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16548,19 +16548,19 @@
         <v>86</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C166" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F166" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16568,19 +16568,19 @@
         <v>87</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C167" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F167" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16600,18 +16600,18 @@
         <v>89</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C169" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="F169" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F169" s="9" t="s">
         <v>298</v>
       </c>
     </row>
@@ -16650,19 +16650,19 @@
         <v>64</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E173" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="174" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16670,19 +16670,19 @@
         <v>80</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F174" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16690,19 +16690,19 @@
         <v>81</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E175" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="176" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16710,19 +16710,19 @@
         <v>84</v>
       </c>
       <c r="B176" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E176" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C176" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="E176" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="F176" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="177" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16742,19 +16742,19 @@
         <v>86</v>
       </c>
       <c r="B178" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E178" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C178" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="E178" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="F178" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="179" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16762,19 +16762,19 @@
         <v>87</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E179" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="180" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -16794,19 +16794,19 @@
         <v>89</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E181" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -16884,7 +16884,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -16917,16 +16917,16 @@
         <v>64</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F5" s="21" t="s">
         <v>168</v>
@@ -16937,16 +16937,16 @@
         <v>80</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>168</v>
@@ -16957,16 +16957,16 @@
         <v>81</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>168</v>
@@ -16977,16 +16977,16 @@
         <v>84</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>168</v>
@@ -17009,16 +17009,16 @@
         <v>86</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>168</v>
@@ -17029,16 +17029,16 @@
         <v>87</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>168</v>
@@ -17061,16 +17061,16 @@
         <v>89</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>168</v>
@@ -17078,7 +17078,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -17111,16 +17111,16 @@
         <v>64</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>168</v>
@@ -17131,16 +17131,16 @@
         <v>80</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>168</v>
@@ -17151,16 +17151,16 @@
         <v>81</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>168</v>
@@ -17171,16 +17171,16 @@
         <v>84</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>168</v>
@@ -17203,16 +17203,16 @@
         <v>86</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>168</v>
@@ -17223,16 +17223,16 @@
         <v>87</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>168</v>
@@ -17255,16 +17255,16 @@
         <v>89</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>168</v>
@@ -17272,7 +17272,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -17305,13 +17305,13 @@
         <v>64</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>169</v>
@@ -17325,13 +17325,13 @@
         <v>80</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>169</v>
@@ -17345,13 +17345,13 @@
         <v>81</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>169</v>
@@ -17365,13 +17365,13 @@
         <v>84</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>169</v>
@@ -17397,13 +17397,13 @@
         <v>86</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E34" s="20" t="s">
         <v>169</v>
@@ -17417,19 +17417,19 @@
         <v>87</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E35" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17449,13 +17449,13 @@
         <v>89</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>169</v>
@@ -17466,7 +17466,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -17508,10 +17508,10 @@
         <v>169</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17528,10 +17528,10 @@
         <v>169</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17548,10 +17548,10 @@
         <v>169</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17568,10 +17568,10 @@
         <v>169</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17600,10 +17600,10 @@
         <v>169</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17620,7 +17620,7 @@
         <v>169</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F47" s="21" t="s">
         <v>168</v>
@@ -17652,7 +17652,7 @@
         <v>169</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F49" s="21" t="s">
         <v>168</v>
@@ -17660,7 +17660,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -17693,10 +17693,10 @@
         <v>64</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D53" s="21" t="s">
         <v>168</v>
@@ -17705,7 +17705,7 @@
         <v>169</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17713,10 +17713,10 @@
         <v>80</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D54" s="21" t="s">
         <v>168</v>
@@ -17725,7 +17725,7 @@
         <v>169</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17733,10 +17733,10 @@
         <v>81</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D55" s="21" t="s">
         <v>168</v>
@@ -17745,7 +17745,7 @@
         <v>169</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17753,10 +17753,10 @@
         <v>84</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D56" s="21" t="s">
         <v>168</v>
@@ -17765,7 +17765,7 @@
         <v>169</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17785,10 +17785,10 @@
         <v>86</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D58" s="21" t="s">
         <v>168</v>
@@ -17797,7 +17797,7 @@
         <v>169</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17808,7 +17808,7 @@
         <v>168</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D59" s="21" t="s">
         <v>168</v>
@@ -17817,7 +17817,7 @@
         <v>169</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17840,7 +17840,7 @@
         <v>168</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D61" s="21" t="s">
         <v>168</v>
@@ -17849,12 +17849,12 @@
         <v>169</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -17887,10 +17887,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D65" s="21" t="s">
         <v>168</v>
@@ -17899,7 +17899,7 @@
         <v>169</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17907,10 +17907,10 @@
         <v>80</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>168</v>
@@ -17919,7 +17919,7 @@
         <v>169</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17927,10 +17927,10 @@
         <v>81</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>168</v>
@@ -17939,7 +17939,7 @@
         <v>169</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17950,7 +17950,7 @@
         <v>168</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>168</v>
@@ -17959,7 +17959,7 @@
         <v>169</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17982,7 +17982,7 @@
         <v>168</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D70" s="21" t="s">
         <v>168</v>
@@ -17991,7 +17991,7 @@
         <v>169</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -17999,10 +17999,10 @@
         <v>87</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D71" s="21" t="s">
         <v>168</v>
@@ -18011,7 +18011,7 @@
         <v>169</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18031,10 +18031,10 @@
         <v>89</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D73" s="21" t="s">
         <v>168</v>
@@ -18043,12 +18043,12 @@
         <v>169</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -18090,10 +18090,10 @@
         <v>168</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18110,10 +18110,10 @@
         <v>168</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18130,10 +18130,10 @@
         <v>168</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18150,10 +18150,10 @@
         <v>168</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18182,10 +18182,10 @@
         <v>168</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18202,10 +18202,10 @@
         <v>168</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18234,15 +18234,15 @@
         <v>168</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F85" s="21" t="s">
-        <v>168</v>
+        <v>278</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -18284,10 +18284,10 @@
         <v>168</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18304,10 +18304,10 @@
         <v>168</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18324,10 +18324,10 @@
         <v>168</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18335,7 +18335,7 @@
         <v>84</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C92" s="20" t="s">
         <v>169</v>
@@ -18344,10 +18344,10 @@
         <v>168</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18367,7 +18367,7 @@
         <v>86</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C94" s="20" t="s">
         <v>169</v>
@@ -18376,10 +18376,10 @@
         <v>168</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18387,7 +18387,7 @@
         <v>87</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C95" s="20" t="s">
         <v>169</v>
@@ -18396,10 +18396,10 @@
         <v>168</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18419,7 +18419,7 @@
         <v>89</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C97" s="20" t="s">
         <v>169</v>
@@ -18428,15 +18428,15 @@
         <v>168</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -18469,19 +18469,19 @@
         <v>64</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18489,19 +18489,19 @@
         <v>80</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18509,19 +18509,19 @@
         <v>81</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18529,19 +18529,19 @@
         <v>84</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18561,19 +18561,19 @@
         <v>86</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18581,19 +18581,19 @@
         <v>87</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E107" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F107" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18613,24 +18613,24 @@
         <v>89</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F109" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -18663,19 +18663,19 @@
         <v>64</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18683,19 +18683,19 @@
         <v>80</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F114" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18703,19 +18703,19 @@
         <v>81</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F115" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="116" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18723,19 +18723,19 @@
         <v>84</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F116" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="117" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18755,19 +18755,19 @@
         <v>86</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F118" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="119" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18775,19 +18775,19 @@
         <v>87</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F119" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="120" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18807,24 +18807,24 @@
         <v>89</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F121" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -18857,19 +18857,19 @@
         <v>64</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="126" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18877,19 +18877,19 @@
         <v>80</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F126" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="127" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18897,19 +18897,19 @@
         <v>81</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="128" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18917,19 +18917,19 @@
         <v>84</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="129" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18949,19 +18949,19 @@
         <v>86</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F130" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="131" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -18969,19 +18969,19 @@
         <v>87</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="132" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19001,24 +19001,24 @@
         <v>89</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -19051,19 +19051,19 @@
         <v>64</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D137" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="138" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19071,19 +19071,19 @@
         <v>80</v>
       </c>
       <c r="B138" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D138" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="139" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19091,19 +19091,19 @@
         <v>81</v>
       </c>
       <c r="B139" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D139" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="140" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19111,19 +19111,19 @@
         <v>84</v>
       </c>
       <c r="B140" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D140" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="141" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19143,19 +19143,19 @@
         <v>86</v>
       </c>
       <c r="B142" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D142" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19163,19 +19163,19 @@
         <v>87</v>
       </c>
       <c r="B143" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D143" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19195,24 +19195,24 @@
         <v>89</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D145" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -19245,19 +19245,19 @@
         <v>64</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D149" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="150" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19265,19 +19265,19 @@
         <v>80</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D150" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F150" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19285,19 +19285,19 @@
         <v>81</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D151" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E151" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19305,19 +19305,19 @@
         <v>84</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D152" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F152" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19337,19 +19337,19 @@
         <v>86</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D154" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E154" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F154" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19357,19 +19357,19 @@
         <v>87</v>
       </c>
       <c r="B155" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D155" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C155" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D155" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="E155" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F155" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19389,24 +19389,24 @@
         <v>89</v>
       </c>
       <c r="B157" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D157" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C157" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D157" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="E157" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F157" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -19439,19 +19439,19 @@
         <v>64</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C161" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D161" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F161" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="162" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19459,19 +19459,19 @@
         <v>80</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C162" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D162" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+      <c r="F162" s="22" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="163" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19479,19 +19479,19 @@
         <v>81</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C163" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D163" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F163" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="164" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19499,19 +19499,19 @@
         <v>84</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C164" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D164" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F164" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="165" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19531,19 +19531,19 @@
         <v>86</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C166" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D166" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F166" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19551,19 +19551,19 @@
         <v>87</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C167" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D167" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F167" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19583,18 +19583,18 @@
         <v>89</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C169" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D169" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="F169" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F169" s="9" t="s">
         <v>298</v>
       </c>
     </row>
@@ -19633,19 +19633,19 @@
         <v>64</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D173" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E173" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="174" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19653,19 +19653,19 @@
         <v>80</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D174" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F174" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="175" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19673,19 +19673,19 @@
         <v>81</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D175" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E175" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="176" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19693,19 +19693,19 @@
         <v>84</v>
       </c>
       <c r="B176" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D176" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C176" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D176" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="E176" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F176" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="177" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19725,19 +19725,19 @@
         <v>86</v>
       </c>
       <c r="B178" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D178" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C178" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="D178" s="20" t="s">
-        <v>293</v>
-      </c>
       <c r="E178" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F178" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="179" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19745,19 +19745,19 @@
         <v>87</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D179" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E179" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="180" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -19777,19 +19777,19 @@
         <v>89</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D181" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E181" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -82,7 +82,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 Performing Arts</t>
+      <t>LA16 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -104,7 +104,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 STEM</t>
+      <t>LA20 STEM</t>
     </r>
     <r>
       <rPr>
@@ -184,17 +184,39 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FF7E57C2"/>
+        <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
+      <t>LA18 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
   </si>
   <si>
@@ -204,7 +226,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 Auslan</t>
+      <t>LA15 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -212,6 +234,66 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P2
+9:40-10:25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
     </r>
     <r>
       <rPr>
@@ -226,7 +308,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA24 Performing Arts</t>
+      <t>LA18 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -235,19 +317,20 @@
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P2
-9:40-10:25</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA19 STEM</t>
+      <t>LA20 STEM</t>
     </r>
     <r>
       <rPr>
@@ -269,7 +352,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Visual Art</t>
+      <t>LA19 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -286,7 +369,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 STEM</t>
+      <t>LA17 STEM</t>
     </r>
     <r>
       <rPr>
@@ -302,13 +385,113 @@
       <t xml:space="preserve">
 </t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 Performing Arts</t>
+      <t>LA22 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -330,7 +513,50 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA18 STEM</t>
+      <t>LA15 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P3
+10:25-11:10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 STEM</t>
     </r>
     <r>
       <rPr>
@@ -352,7 +578,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 Visual Art</t>
+      <t>LA21 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -369,7 +595,90 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 STEM</t>
+      <t>LA9 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 STEM</t>
     </r>
     <r>
       <rPr>
@@ -410,17 +719,100 @@
     <r>
       <rPr>
         <b/>
-        <color rgb="FFD98A3D"/>
+        <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
+      <t>LA24 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
         <sz val="9"/>
       </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA17 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -435,7 +827,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 Performing Arts</t>
+      <t>LA14 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -446,13 +838,35 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA6 PE</t>
+      <t>LA15 STEM</t>
     </r>
     <r>
       <rPr>
@@ -474,7 +888,262 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA8 PE</t>
+      <t>LA21 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch
+11:10-11:50</t>
+  </si>
+  <si>
+    <t>Lunch (11:10-11:50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4
+11:50-12:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA15 PE</t>
     </r>
     <r>
       <rPr>
@@ -496,7 +1165,7 @@
         <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 PE</t>
+      <t>LA21 PE</t>
     </r>
     <r>
       <rPr>
@@ -518,7 +1187,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 Auslan</t>
+      <t>LA8 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -527,15 +1196,59 @@
       </rPr>
       <t xml:space="preserve">  Rachel Walker</t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA22 Auslan</t>
+      <t>LA20 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA19 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -566,6 +1279,254 @@
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P5
+12:35-1:20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA23 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA16 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF29A39A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF29A39A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA6 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA9 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA21 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
     <r>
       <rPr>
         <sz val="6"/>
@@ -579,7 +1540,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 Health</t>
+      <t>LA19 PE</t>
     </r>
     <r>
       <rPr>
@@ -588,19 +1549,153 @@
       </rPr>
       <t xml:space="preserve">  Aaron Bell</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P3
-10:25-11:10</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF6AA9E0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 PE</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF6AA9E0"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Jake Pevitt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA7 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA22 Performing Arts</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF4A90D9"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA18 Health</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF4A90D9"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Aaron Bell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD4538A"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA20 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD4538A"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA19 STEM</t>
+      <t>LA24 STEM</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F8A82"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Lis Lowndes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Recess
+1:20-1:35</t>
+  </si>
+  <si>
+    <t>Recess (1:20-1:35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6
+1:35-2:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1F8A82"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA24 Health</t>
     </r>
     <r>
       <rPr>
@@ -622,7 +1717,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA15 Visual Art</t>
+      <t>LA20 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -639,7 +1734,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA9 STEM</t>
+      <t>LA6 STEM</t>
     </r>
     <r>
       <rPr>
@@ -661,7 +1756,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 Performing Arts</t>
+      <t>LA19 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -683,7 +1778,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 STEM</t>
+      <t>LA22 STEM</t>
     </r>
     <r>
       <rPr>
@@ -705,7 +1800,7 @@
         <color rgb="FFD98A3D"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 Visual Art</t>
+      <t>LA17 Visual Art</t>
     </r>
     <r>
       <rPr>
@@ -722,7 +1817,7 @@
         <color rgb="FF29A39A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 STEM</t>
+      <t>LA7 STEM</t>
     </r>
     <r>
       <rPr>
@@ -730,6 +1825,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Chantel Uhe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF7E57C2"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA14 Auslan</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF7E57C2"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Rachel Walker</t>
     </r>
     <r>
       <rPr>
@@ -744,7 +1861,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA19 Performing Arts</t>
+      <t>LA15 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -752,6 +1869,28 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFD98A3D"/>
+        <sz val="10"/>
+      </rPr>
+      <t>LA8 Visual Art</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD98A3D"/>
+        <sz val="9"/>
+      </rPr>
+      <t xml:space="preserve">  Natalie Carter</t>
     </r>
     <r>
       <rPr>
@@ -766,7 +1905,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA20 STEM</t>
+      <t>LA21 STEM</t>
     </r>
     <r>
       <rPr>
@@ -774,28 +1913,6 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
     </r>
   </si>
   <si>
@@ -805,7 +1922,7 @@
         <color rgb="FF1F8A82"/>
         <sz val="10"/>
       </rPr>
-      <t>LA7 PE</t>
+      <t>LA22 PE</t>
     </r>
     <r>
       <rPr>
@@ -827,7 +1944,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA16 PE</t>
+      <t>LA23 PE</t>
     </r>
     <r>
       <rPr>
@@ -849,7 +1966,7 @@
         <color rgb="FF6AA9E0"/>
         <sz val="10"/>
       </rPr>
-      <t>LA17 PE</t>
+      <t>LA24 PE</t>
     </r>
     <r>
       <rPr>
@@ -871,7 +1988,7 @@
         <color rgb="FF7E57C2"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Auslan</t>
+      <t>LA16 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -893,7 +2010,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA14 Performing Arts</t>
+      <t>LA9 Performing Arts</t>
     </r>
     <r>
       <rPr>
@@ -910,7 +2027,7 @@
         <color rgb="FFD4538A"/>
         <sz val="10"/>
       </rPr>
-      <t>LA23 Auslan</t>
+      <t>LA18 Auslan</t>
     </r>
     <r>
       <rPr>
@@ -918,28 +2035,6 @@
         <sz val="9"/>
       </rPr>
       <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
     </r>
     <r>
       <rPr>
@@ -954,7 +2049,7 @@
         <color rgb="FF4A90D9"/>
         <sz val="10"/>
       </rPr>
-      <t>LA21 Health</t>
+      <t>LA23 Health</t>
     </r>
     <r>
       <rPr>
@@ -965,1101 +2060,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Lunch
-11:10-11:50</t>
-  </si>
-  <si>
-    <t>Lunch (11:10-11:50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4
-11:50-12:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P5
-12:35-1:20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Recess
-1:20-1:35</t>
-  </si>
-  <si>
-    <t>Recess (1:20-1:35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6
-1:35-2:35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA8 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA6 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA17 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA19 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF29A39A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA7 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF29A39A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Chantel Uhe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA14 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA15 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD98A3D"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA9 Visual Art</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD98A3D"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Natalie Carter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA21 STEM</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF1F8A82"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA22 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1F8A82"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Lis Lowndes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF6AA9E0"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA24 PE</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF6AA9E0"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Jake Pevitt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF7E57C2"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA16 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF7E57C2"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Rachel Walker</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA18 Performing Arts</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FFD4538A"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA20 Auslan</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FFD4538A"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Cheryl Peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF4A90D9"/>
-        <sz val="10"/>
-      </rPr>
-      <t>LA23 Health</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF4A90D9"/>
-        <sz val="9"/>
-      </rPr>
-      <t xml:space="preserve">  Aaron Bell</t>
-    </r>
-  </si>
-  <si>
     <t>Mon · whole school (specialist in colour, otherwise classroom teacher)</t>
   </si>
   <si>
@@ -2177,14 +2177,14 @@
     <t>P2 9:40-10:25</t>
   </si>
   <si>
+    <t xml:space="preserve">Visual Art
+Natalie Carter</t>
+  </si>
+  <si>
     <t xml:space="preserve">STEM
 Lis Lowndes</t>
   </si>
   <si>
-    <t xml:space="preserve">Visual Art
-Natalie Carter</t>
-  </si>
-  <si>
     <t>P3 10:25-11:10</t>
   </si>
   <si>
@@ -2307,37 +2307,37 @@
 Performing Arts · Peak</t>
   </si>
   <si>
+    <t xml:space="preserve">DOTT (release)
+Visual Art · Carter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOTT (release)
+PE · Lowndes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOTT (release)
+STEM · Uhe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Collaboration
 Y5-6 meeting</t>
   </si>
   <si>
-    <t xml:space="preserve">DOTT (release)
-PE · Lowndes</t>
+    <t>Nicola Pigott  ·  classroom teacher (LA7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA7
+own class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration
+Y4-5 meeting</t>
   </si>
   <si>
     <t xml:space="preserve">DOTT (release)
 Auslan · Walker</t>
   </si>
   <si>
-    <t xml:space="preserve">DOTT (release)
-STEM · Uhe</t>
-  </si>
-  <si>
-    <t>Nicola Pigott  ·  classroom teacher (LA7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7
-own class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOTT (release)
-Visual Art · Carter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaboration
-Y4-5 meeting</t>
-  </si>
-  <si>
     <t>Janette Crisp  ·  classroom teacher (LA8)</t>
   </si>
   <si>
@@ -2513,23 +2513,47 @@
     <t>Lis Lowndes  ·  specialist (1.0; works Mon/Tue/Wed/Thu/Fri)</t>
   </si>
   <si>
+    <t xml:space="preserve">LA20 (2)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration
+STEM/PE team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cover T9
+(Dyer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+STEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA7 (5)
+PE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA18 (2)
 STEM</t>
   </si>
   <si>
-    <t xml:space="preserve">Collaboration
-STEM/PE team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cover T9
-(Dyer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA19 (2)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA6 (5/6)
+    <t xml:space="preserve">LA14 (3/4)
 PE</t>
   </si>
   <si>
@@ -2537,30 +2561,6 @@
 STEM</t>
   </si>
   <si>
-    <t xml:space="preserve">LA14 (3/4)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA20 (2)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7 (5)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-STEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-STEM</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA22 (1)
 STEM</t>
   </si>
@@ -2596,79 +2596,119 @@
 Visual Art</t>
   </si>
   <si>
+    <t xml:space="preserve">LA18 (2)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collaboration
+Arts team</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA21 (3)
 Visual Art</t>
   </si>
   <si>
+    <t xml:space="preserve">LA7 (5)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA16 (4)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA9 (5/6)
+Visual Art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA20 (2)
+Visual Art</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA17 (4/5)
 Visual Art</t>
   </si>
   <si>
-    <t xml:space="preserve">LA6 (5/6)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA7 (5)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA16 (4)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA20 (2)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA14 (3/4)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaboration
-Arts team</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA8 (6)
 Visual Art</t>
   </si>
   <si>
-    <t xml:space="preserve">LA19 (2)
-Visual Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA9 (5/6)
-Visual Art</t>
-  </si>
-  <si>
     <t>Cheryl Peak  ·  specialist (0.8; works Tue/Wed/Thu/Fri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA16 (4)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA6 (5/6)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leadership
+Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA18 (2)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA22 (1)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA17 (4/5)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24 (1)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA14 (3/4)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA23 (1)
+Performing Arts</t>
   </si>
   <si>
     <t xml:space="preserve">LA20 (2)
 Performing Arts</t>
   </si>
   <si>
-    <t xml:space="preserve">LA6 (5/6)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24 (1)
-Performing Arts</t>
+    <t xml:space="preserve">LA19 (2)
+Auslan</t>
   </si>
   <si>
     <t xml:space="preserve">LA7 (5)
@@ -2680,30 +2720,18 @@
   </si>
   <si>
     <t xml:space="preserve">LA22 (1)
+Performing Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA20 (2)
 Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA16 (4)
-Performing Arts</t>
   </si>
   <si>
     <t xml:space="preserve">LA19 (2)
 Performing Arts</t>
   </si>
   <si>
-    <t xml:space="preserve">LA14 (3/4)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA23 (1)
+    <t xml:space="preserve">LA15 (3)
 Performing Arts</t>
   </si>
   <si>
@@ -2711,73 +2739,45 @@
 Performing Arts</t>
   </si>
   <si>
-    <t xml:space="preserve">LA19 (2)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leadership
-Events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Performing Arts</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA18 (2)
 Auslan</t>
   </si>
   <si>
+    <t>Rachel Walker  ·  specialist (0.4; works Wed/Thu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA15 (3)
+Auslan</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA17 (4/5)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA18 (2)
-Performing Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA20 (2)
 Auslan</t>
   </si>
   <si>
-    <t>Rachel Walker  ·  specialist (0.4; works Wed/Thu)</t>
+    <t xml:space="preserve">LA9 (5/6)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA21 (3)
+Auslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA24 (1)
+Auslan</t>
   </si>
   <si>
     <t xml:space="preserve">LA8 (6)
 Auslan</t>
   </si>
   <si>
+    <t xml:space="preserve">LA6 (5/6)
+Auslan</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA7 (5)
 Auslan</t>
   </si>
   <si>
-    <t xml:space="preserve">LA9 (5/6)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA15 (3)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA21 (3)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA24 (1)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA6 (5/6)
-Auslan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA17 (4/5)
-Auslan</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA14 (3/4)
 Auslan</t>
   </si>
@@ -2809,18 +2809,18 @@
 PE</t>
   </si>
   <si>
+    <t xml:space="preserve">LA22 (1)
+Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA19 (2)
+PE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LA18 (2)
 Health</t>
   </si>
   <si>
-    <t xml:space="preserve">LA19 (2)
-PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA22 (1)
-Health</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA23 (1)
 PE</t>
   </si>
@@ -3007,7 +3007,7 @@
     <t>| Y1 | Wed P4 | LA22: Imogen Webb (Visual Art/Carter); LA23: Ashlee Hutchings (Performing Arts/Peak); LA24: Chloe Moore (Auslan/Walker) | PASS |</t>
   </si>
   <si>
-    <t>| Y2 | Wed P3 | LA18: Hannah Bouwmeester (Visual Art/Carter); LA19: Savannah Espach (Performing Arts/Peak); LA20: Anna Hendron (STEM/Lowndes) | PASS |</t>
+    <t>| Y2 | Tue P2 | LA18: Hannah Bouwmeester (Performing Arts/Peak); LA19: Savannah Espach (Visual Art/Carter); LA20: Anna Hendron (STEM/Lowndes) | PASS |</t>
   </si>
   <si>
     <t>| Y3-4 | Thu P4 | LA14: Olivia Sheehy (PE/Lowndes); LA15: Georgia Mitchell (PE/Bell); LA21: Jasper Sirr-Davis (PE/Pevitt) | PASS |</t>
@@ -3016,10 +3016,10 @@
     <t>| Y4-5 | Thu P3 | LA7: Nicola Pigott (PE/Lowndes); LA16: Tanya Thieme (PE/Bell); LA17: Cassidy Law (PE/Pevitt) | PASS |</t>
   </si>
   <si>
-    <t>| Y5-6 | Wed P2 | LA6: John Dunbar (Visual Art/Carter); LA8: Janette Crisp (Performing Arts/Peak); LA9: Lincoln Rose (Auslan/Walker) | PASS |</t>
-  </si>
-  <si>
-    <t>| Arts | Wed P5 | Peak, Carter, Walker all on DOTT | PASS |</t>
+    <t>| Y5-6 | Wed P5 | LA6: John Dunbar (Auslan/Walker); LA8: Janette Crisp (Performing Arts/Peak); LA9: Lincoln Rose (Visual Art/Carter) | PASS |</t>
+  </si>
+  <si>
+    <t>| Arts | Wed P2 | Peak, Carter, Walker all on DOTT | PASS |</t>
   </si>
   <si>
     <t>| STEM/PE | Thu P1 | Bell, Lowndes on DOTT; Uhe joins from Thursday office | PASS |</t>
@@ -3037,16 +3037,16 @@
     <t>| --- | --- | --- | --- | --- |</t>
   </si>
   <si>
+    <t>| Mon | LA20 | Visual Art | Natalie Carter | base release |</t>
+  </si>
+  <si>
     <t>| Mon | LA24 | Health | Lis Lowndes | grad extra |</t>
   </si>
   <si>
-    <t>| Mon | LA8 | Visual Art | Natalie Carter | base release |</t>
-  </si>
-  <si>
-    <t>| Tue | LA17 | Performing Arts | Cheryl Peak | base release |</t>
-  </si>
-  <si>
-    <t>| Tue | LA19 | Visual Art | Natalie Carter | base release |</t>
+    <t>| Tue | LA17 | Visual Art | Natalie Carter | base release |</t>
+  </si>
+  <si>
+    <t>| Tue | LA19 | Performing Arts | Cheryl Peak | base release |</t>
   </si>
   <si>
     <t>| Tue | LA22 | STEM | Lis Lowndes | base release |</t>
@@ -3067,15 +3067,12 @@
     <t>| Wed | LA7 | STEM | Chantel Uhe | base release |</t>
   </si>
   <si>
-    <t>| Wed | LA9 | Visual Art | Natalie Carter | base release |</t>
+    <t>| Wed | LA8 | Visual Art | Natalie Carter | base release |</t>
   </si>
   <si>
     <t>| Thu | LA16 | Auslan | Rachel Walker | base release |</t>
   </si>
   <si>
-    <t>| Thu | LA18 | Performing Arts | Cheryl Peak | base release |</t>
-  </si>
-  <si>
     <t>| Thu | LA22 | PE | Lis Lowndes | base release |</t>
   </si>
   <si>
@@ -3085,7 +3082,10 @@
     <t>| Thu | LA24 | PE | Jake Pevitt | base release |</t>
   </si>
   <si>
-    <t>| Fri | LA20 | Auslan | Cheryl Peak | base release |</t>
+    <t>| Thu | LA9 | Performing Arts | Cheryl Peak | base release |</t>
+  </si>
+  <si>
+    <t>| Fri | LA18 | Auslan | Cheryl Peak | base release |</t>
   </si>
   <si>
     <t>| Fri | LA23 | Health | Aaron Bell | grad extra |</t>
@@ -3103,7 +3103,7 @@
     <t>| Natalie Carter | PBS | Mon P1 | fixed (moved from Mon P3 so LA23 can take P3 - Brad item 5) |</t>
   </si>
   <si>
-    <t>| Cheryl Peak | Events | Tue P5 | Peak non-teaching block |</t>
+    <t>| Cheryl Peak | Events | Fri P1 | leads the Friday assembly (P1 carries no specialist teaching) |</t>
   </si>
   <si>
     <t>| Lincoln Rose | SSTUWA | Fri P2 | LA9 covered by Aaron Bell (Health) · additional 45-min release on top of normal DOTT |</t>
@@ -3307,37 +3307,37 @@
     <t>| --- | --- | --- | --- | --- | --- | --- |</t>
   </si>
   <si>
-    <t>| LA6 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
+    <t>| LA6 | 1 | 2 | 2 | 1 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA7 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
-    <t>| LA8 | 1 | 2 | 2 | 1 | 0 | 2 |</t>
+    <t>| LA8 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA9 | 0 | 2 | 2 | 2 | 1 | 2 |</t>
   </si>
   <si>
-    <t>| LA14 | 1 | 2 | 1 | 2 | 0 | 2 |</t>
+    <t>| LA14 | 2 | 1 | 1 | 2 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA15 | 1 | 0 | 1 | 2 | 2 | 2 |</t>
   </si>
   <si>
-    <t>| LA16 | 1 | 1 | 2 | 2 | 0 | 2 |</t>
+    <t>| LA16 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
     <t>| LA17 | 0 | 2 | 2 | 2 | 0 | 2 |</t>
   </si>
   <si>
-    <t>| LA18 | 0 | 2 | 1 | 2 | 2 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA19 | 2 | 1 | 1 | 1 | 1 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA20 | 0 | 2 | 2 | 1 | 1 | 2 |</t>
+    <t>| LA18 | 2 | 1 | 1 | 1 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA19 | 0 | 2 | 2 | 1 | 1 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA20 | 1 | 2 | 0 | 2 | 1 | 2 |</t>
   </si>
   <si>
     <t>| LA21 | 1 | 1 | 2 | 2 | 1 | 2 |</t>
@@ -3346,10 +3346,10 @@
     <t>| LA22 | 0 | 2 | 1 | 2 | 2 | 2 |</t>
   </si>
   <si>
-    <t>| LA23 | 2 | 1 | 1 | 1 | 2 | 2 |</t>
-  </si>
-  <si>
-    <t>| LA24 | 1 | 1 | 1 | 2 | 2 | 2 |</t>
+    <t>| LA23 | 1 | 2 | 1 | 1 | 2 | 2 |</t>
+  </si>
+  <si>
+    <t>| LA24 | 1 | 1 | 2 | 1 | 2 | 2 |</t>
   </si>
   <si>
     <t>Within the daily cap (2 per class, 3 for the two leadership classes on their leadership day): PASS.</t>
@@ -3385,7 +3385,7 @@
     <t>STEM (rule 5): every STEM block is two back-to-back periods (consecutive period numbers, same day): PASS.</t>
   </si>
   <si>
-    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:9  P2:17  P3:18  P4:19  P5:15  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
+    <t>Specialist teaching by period (rule 7 aims to keep mornings lighter for literacy): P1:9  P2:15  P3:17  P4:18  P5:19  P6:18. Note Thursday PE necessarily fills some morning slots; the rest of the week is pushed later where the other hard rules allow.</t>
   </si>
   <si>
     <t>10. Pre-Primary &amp; Kindy DOTT ledger</t>
@@ -3518,12 +3518,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8A82"/>
+        <fgColor rgb="FFD98A3D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD98A3D"/>
+        <fgColor rgb="FF1F8A82"/>
       </patternFill>
     </fill>
     <fill>
@@ -4388,8 +4388,8 @@
       <c r="A5" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>65</v>
+      <c r="B5" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>66</v>
@@ -4400,8 +4400,8 @@
       <c r="E5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>69</v>
+      <c r="F5" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>70</v>
@@ -4415,14 +4415,14 @@
       <c r="J5" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>82</v>
+      <c r="K5" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>83</v>
+      <c r="M5" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>77</v>
@@ -4450,11 +4450,11 @@
       <c r="E6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>83</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>71</v>
@@ -4465,14 +4465,14 @@
       <c r="J6" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>82</v>
+      <c r="K6" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="9" t="s">
-        <v>76</v>
+      <c r="M6" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>77</v>
@@ -4525,17 +4525,17 @@
       <c r="F8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>83</v>
+      <c r="G8" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>73</v>
+      <c r="J8" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>74</v>
@@ -4549,8 +4549,8 @@
       <c r="N8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="10" t="s">
-        <v>82</v>
+      <c r="O8" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P8" s="9" t="s">
         <v>79</v>
@@ -4572,8 +4572,8 @@
       <c r="E9" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>83</v>
+      <c r="F9" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>70</v>
@@ -4584,8 +4584,8 @@
       <c r="I9" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>73</v>
+      <c r="J9" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>74</v>
@@ -4638,8 +4638,8 @@
       <c r="C11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>83</v>
+      <c r="D11" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>68</v>
@@ -4662,8 +4662,8 @@
       <c r="K11" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>75</v>
+      <c r="L11" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>76</v>
@@ -4674,7 +4674,7 @@
       <c r="O11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="11" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4820,20 +4820,20 @@
       <c r="G16" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>71</v>
+      <c r="H16" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>82</v>
+      <c r="J16" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>93</v>
+      <c r="L16" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>76</v>
@@ -4844,8 +4844,8 @@
       <c r="O16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>83</v>
+      <c r="P16" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4855,8 +4855,8 @@
       <c r="B17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>93</v>
+      <c r="C17" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>92</v>
@@ -4873,17 +4873,17 @@
       <c r="H17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>76</v>
@@ -4905,8 +4905,8 @@
       <c r="B18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>83</v>
+      <c r="C18" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>67</v>
@@ -4914,17 +4914,17 @@
       <c r="E18" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>82</v>
+      <c r="F18" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>73</v>
@@ -4941,8 +4941,8 @@
       <c r="N18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O18" s="9" t="s">
-        <v>78</v>
+      <c r="O18" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="P18" s="9" t="s">
         <v>79</v>
@@ -5004,8 +5004,8 @@
       <c r="K20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L20" s="11" t="s">
-        <v>83</v>
+      <c r="L20" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>93</v>
@@ -5013,8 +5013,8 @@
       <c r="N20" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="O20" s="9" t="s">
-        <v>78</v>
+      <c r="O20" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="P20" s="9" t="s">
         <v>79</v>
@@ -5027,8 +5027,8 @@
       <c r="B21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>66</v>
+      <c r="C21" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>67</v>
@@ -5042,8 +5042,8 @@
       <c r="G21" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>71</v>
+      <c r="H21" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>72</v>
@@ -5060,11 +5060,11 @@
       <c r="M21" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N21" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="O21" s="11" t="s">
+      <c r="N21" s="11" t="s">
         <v>83</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>79</v>
@@ -5117,14 +5117,14 @@
       <c r="H23" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>93</v>
+      <c r="I23" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K23" s="11" t="s">
-        <v>83</v>
+      <c r="K23" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>75</v>
@@ -5132,8 +5132,8 @@
       <c r="M23" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N23" s="10" t="s">
-        <v>82</v>
+      <c r="N23" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>78</v>
@@ -5272,8 +5272,8 @@
       <c r="C28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>95</v>
+      <c r="D28" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>68</v>
@@ -5290,11 +5290,11 @@
       <c r="I28" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>74</v>
+      <c r="J28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>75</v>
@@ -5316,17 +5316,17 @@
       <c r="A29" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>83</v>
+      <c r="B29" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>95</v>
+      <c r="D29" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>69</v>
@@ -5343,8 +5343,8 @@
       <c r="J29" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>74</v>
+      <c r="K29" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="L29" s="9" t="s">
         <v>75</v>
@@ -5375,8 +5375,8 @@
       <c r="D30" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>68</v>
+      <c r="E30" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>69</v>
@@ -5390,14 +5390,14 @@
       <c r="I30" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J30" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>82</v>
+      <c r="J30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M30" s="9" t="s">
         <v>76</v>
@@ -5408,8 +5408,8 @@
       <c r="O30" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P30" s="9" t="s">
-        <v>79</v>
+      <c r="P30" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -5468,14 +5468,14 @@
       <c r="K32" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L32" s="10" t="s">
-        <v>82</v>
+      <c r="L32" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N32" s="11" t="s">
-        <v>83</v>
+      <c r="N32" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="O32" s="13" t="s">
         <v>93</v>
@@ -5488,17 +5488,17 @@
       <c r="A33" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>65</v>
+      <c r="B33" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>68</v>
+      <c r="D33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>69</v>
@@ -5521,8 +5521,8 @@
       <c r="L33" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M33" s="10" t="s">
-        <v>82</v>
+      <c r="M33" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>77</v>
@@ -5566,11 +5566,11 @@
       <c r="C35" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>83</v>
+      <c r="D35" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>95</v>
@@ -5593,8 +5593,8 @@
       <c r="L35" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M35" s="10" t="s">
-        <v>82</v>
+      <c r="M35" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>77</v>
@@ -5733,8 +5733,8 @@
       <c r="B40" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>95</v>
+      <c r="C40" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>67</v>
@@ -5745,8 +5745,8 @@
       <c r="F40" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G40" s="9" t="s">
-        <v>70</v>
+      <c r="G40" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>71</v>
@@ -5772,15 +5772,15 @@
       <c r="O40" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P40" s="13" t="s">
-        <v>93</v>
+      <c r="P40" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="11" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="9" t="s">
@@ -5795,14 +5795,14 @@
       <c r="F41" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G41" s="14" t="s">
-        <v>95</v>
+      <c r="G41" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I41" s="9" t="s">
-        <v>72</v>
+      <c r="I41" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>73</v>
@@ -5833,7 +5833,7 @@
       <c r="B42" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="11" t="s">
         <v>97</v>
       </c>
       <c r="D42" s="9" t="s">
@@ -5902,19 +5902,19 @@
       <c r="A44" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>95</v>
+      <c r="B44" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="10" t="s">
+      <c r="D44" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>97</v>
       </c>
       <c r="G44" s="15" t="s">
@@ -5932,8 +5932,8 @@
       <c r="K44" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L44" s="9" t="s">
-        <v>75</v>
+      <c r="L44" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="M44" s="16" t="s">
         <v>99</v>
@@ -5955,8 +5955,8 @@
       <c r="B45" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="9" t="s">
-        <v>66</v>
+      <c r="C45" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>67</v>
@@ -5973,10 +5973,10 @@
       <c r="H45" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I45" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="J45" s="10" t="s">
+      <c r="I45" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45" s="11" t="s">
         <v>97</v>
       </c>
       <c r="K45" s="15" t="s">
@@ -6033,8 +6033,8 @@
       <c r="D47" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E47" s="9" t="s">
-        <v>68</v>
+      <c r="E47" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>69</v>
@@ -6048,8 +6048,8 @@
       <c r="I47" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J47" s="13" t="s">
-        <v>93</v>
+      <c r="J47" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>74</v>
@@ -6060,7 +6060,7 @@
       <c r="M47" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N47" s="10" t="s">
+      <c r="N47" s="11" t="s">
         <v>97</v>
       </c>
       <c r="O47" s="15" t="s">
@@ -6259,8 +6259,8 @@
       <c r="F53" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G53" s="9" t="s">
-        <v>70</v>
+      <c r="G53" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="H53" s="9" t="s">
         <v>71</v>
@@ -6286,8 +6286,8 @@
       <c r="O53" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P53" s="10" t="s">
-        <v>82</v>
+      <c r="P53" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -6309,8 +6309,8 @@
       <c r="F54" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>70</v>
+      <c r="G54" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>71</v>
@@ -6336,8 +6336,8 @@
       <c r="O54" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="P54" s="10" t="s">
-        <v>82</v>
+      <c r="P54" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -6381,8 +6381,8 @@
       <c r="F56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>82</v>
+      <c r="G56" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>71</v>
@@ -6390,8 +6390,8 @@
       <c r="I56" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J56" s="15" t="s">
-        <v>101</v>
+      <c r="J56" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="K56" s="13" t="s">
         <v>102</v>
@@ -6402,14 +6402,14 @@
       <c r="M56" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N56" s="9" t="s">
-        <v>77</v>
+      <c r="N56" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="O56" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P56" s="9" t="s">
-        <v>79</v>
+      <c r="P56" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -6431,8 +6431,8 @@
       <c r="F57" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>82</v>
+      <c r="G57" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>71</v>
@@ -6440,26 +6440,26 @@
       <c r="I57" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J57" s="13" t="s">
-        <v>102</v>
+      <c r="J57" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L57" s="9" t="s">
-        <v>75</v>
+      <c r="L57" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="M57" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N57" s="15" t="s">
-        <v>101</v>
+      <c r="N57" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P57" s="9" t="s">
-        <v>79</v>
+      <c r="P57" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -6512,14 +6512,14 @@
       <c r="I59" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J59" s="9" t="s">
-        <v>73</v>
+      <c r="J59" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L59" s="13" t="s">
-        <v>102</v>
+      <c r="L59" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="M59" s="9" t="s">
         <v>76</v>
@@ -6640,16 +6640,16 @@
       <c r="A5" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>65</v>
+      <c r="B5" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>97</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -6701,8 +6701,8 @@
       <c r="D8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>95</v>
+      <c r="E8" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>65</v>
@@ -6718,8 +6718,8 @@
       <c r="C9" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>65</v>
+      <c r="D9" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>65</v>
@@ -6823,8 +6823,8 @@
       <c r="D16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>95</v>
+      <c r="E16" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>66</v>
@@ -6837,8 +6837,8 @@
       <c r="B17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>93</v>
+      <c r="C17" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>66</v>
@@ -6857,13 +6857,13 @@
       <c r="B18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>83</v>
+      <c r="C18" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>97</v>
       </c>
       <c r="F18" s="9" t="s">
@@ -6909,14 +6909,14 @@
       <c r="B21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>66</v>
+      <c r="C21" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>66</v>
+      <c r="E21" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>66</v>
@@ -7014,8 +7014,8 @@
       <c r="C28" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>95</v>
+      <c r="D28" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>67</v>
@@ -7034,8 +7034,8 @@
       <c r="C29" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>93</v>
+      <c r="D29" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>98</v>
@@ -7089,8 +7089,8 @@
       <c r="D32" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>67</v>
+      <c r="E32" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>67</v>
@@ -7106,8 +7106,8 @@
       <c r="C33" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>67</v>
+      <c r="D33" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>67</v>
@@ -7132,14 +7132,14 @@
       <c r="A35" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>83</v>
+      <c r="B35" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>67</v>
+      <c r="D35" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>67</v>
@@ -7228,8 +7228,8 @@
       <c r="C41" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="14" t="s">
-        <v>95</v>
+      <c r="D41" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>99</v>
@@ -7248,8 +7248,8 @@
       <c r="C42" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>68</v>
+      <c r="D42" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>68</v>
@@ -7283,8 +7283,8 @@
       <c r="D44" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="13" t="s">
-        <v>93</v>
+      <c r="E44" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>68</v>
@@ -7300,8 +7300,8 @@
       <c r="C45" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>68</v>
+      <c r="D45" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>68</v>
@@ -7332,11 +7332,11 @@
       <c r="C47" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E47" s="9" t="s">
+      <c r="D47" s="9" t="s">
         <v>68</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
@@ -7416,8 +7416,8 @@
       <c r="A53" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>69</v>
+      <c r="B53" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>69</v>
@@ -7436,11 +7436,11 @@
       <c r="A54" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>69</v>
@@ -7477,7 +7477,7 @@
       <c r="D56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="11" t="s">
         <v>97</v>
       </c>
       <c r="F56" s="9" t="s">
@@ -7488,8 +7488,8 @@
       <c r="A57" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="11" t="s">
-        <v>83</v>
+      <c r="B57" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>69</v>
@@ -7599,8 +7599,8 @@
       <c r="D64" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>70</v>
+      <c r="E64" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>70</v>
@@ -7619,19 +7619,19 @@
       <c r="D65" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E65" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F65" s="9" t="s">
+      <c r="E65" s="9" t="s">
         <v>70</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>83</v>
+      <c r="B66" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>70</v>
@@ -7642,8 +7642,8 @@
       <c r="E66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="9" t="s">
-        <v>70</v>
+      <c r="F66" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7662,8 +7662,8 @@
       <c r="A68" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>70</v>
+      <c r="B68" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>70</v>
@@ -7674,8 +7674,8 @@
       <c r="E68" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F68" s="10" t="s">
-        <v>82</v>
+      <c r="F68" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7694,8 +7694,8 @@
       <c r="E69" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>82</v>
+      <c r="F69" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7787,8 +7787,8 @@
       <c r="B76" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>71</v>
+      <c r="C76" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>71</v>
@@ -7827,8 +7827,8 @@
       <c r="B78" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>93</v>
+      <c r="C78" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>92</v>
@@ -7856,8 +7856,8 @@
       <c r="A80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="11" t="s">
-        <v>83</v>
+      <c r="B80" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>71</v>
@@ -7879,8 +7879,8 @@
       <c r="B81" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>71</v>
+      <c r="C81" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>71</v>
@@ -8001,14 +8001,14 @@
       <c r="B89" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>83</v>
+      <c r="C89" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E89" s="9" t="s">
-        <v>72</v>
+      <c r="E89" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>72</v>
@@ -8021,8 +8021,8 @@
       <c r="B90" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>72</v>
+      <c r="C90" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>72</v>
@@ -8079,8 +8079,8 @@
       <c r="D93" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E93" s="14" t="s">
-        <v>95</v>
+      <c r="E93" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>72</v>
@@ -8105,8 +8105,8 @@
       <c r="B95" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C95" s="13" t="s">
-        <v>93</v>
+      <c r="C95" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>72</v>
@@ -8175,11 +8175,11 @@
       <c r="B100" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D100" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>73</v>
@@ -8195,8 +8195,8 @@
       <c r="B101" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>82</v>
+      <c r="C101" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>73</v>
@@ -8218,8 +8218,8 @@
       <c r="C102" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D102" s="11" t="s">
-        <v>83</v>
+      <c r="D102" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>73</v>
@@ -8244,8 +8244,8 @@
       <c r="A104" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B104" s="9" t="s">
-        <v>73</v>
+      <c r="B104" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>73</v>
@@ -8256,16 +8256,16 @@
       <c r="E104" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F104" s="15" t="s">
-        <v>101</v>
+      <c r="F104" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B105" s="9" t="s">
-        <v>73</v>
+      <c r="B105" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>73</v>
@@ -8273,11 +8273,11 @@
       <c r="D105" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F105" s="13" t="s">
-        <v>102</v>
+      <c r="F105" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8305,11 +8305,11 @@
       <c r="D107" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E107" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F107" s="9" t="s">
+      <c r="E107" s="9" t="s">
         <v>73</v>
+      </c>
+      <c r="F107" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -8372,8 +8372,8 @@
       <c r="C112" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D112" s="9" t="s">
-        <v>74</v>
+      <c r="D112" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>74</v>
@@ -8386,14 +8386,14 @@
       <c r="A113" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B113" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C113" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C113" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>74</v>
+      <c r="D113" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>74</v>
@@ -8406,14 +8406,14 @@
       <c r="A114" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>82</v>
+      <c r="B114" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D114" s="13" t="s">
-        <v>93</v>
+      <c r="D114" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>74</v>
@@ -8493,8 +8493,8 @@
       <c r="B119" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C119" s="11" t="s">
-        <v>83</v>
+      <c r="C119" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>74</v>
@@ -8563,8 +8563,8 @@
       <c r="B124" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C124" s="13" t="s">
-        <v>93</v>
+      <c r="C124" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>75</v>
@@ -8583,8 +8583,8 @@
       <c r="B125" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C125" s="9" t="s">
-        <v>75</v>
+      <c r="C125" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>75</v>
@@ -8606,8 +8606,8 @@
       <c r="C126" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D126" s="10" t="s">
-        <v>82</v>
+      <c r="D126" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>75</v>
@@ -8635,14 +8635,14 @@
       <c r="B128" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C128" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E128" s="9" t="s">
+      <c r="C128" s="9" t="s">
         <v>75</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>75</v>
@@ -8664,8 +8664,8 @@
       <c r="E129" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F129" s="9" t="s">
-        <v>75</v>
+      <c r="F129" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="130" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8684,8 +8684,8 @@
       <c r="A131" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B131" s="9" t="s">
-        <v>75</v>
+      <c r="B131" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>75</v>
@@ -8696,8 +8696,8 @@
       <c r="E131" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F131" s="13" t="s">
-        <v>102</v>
+      <c r="F131" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -8774,8 +8774,8 @@
       <c r="A137" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B137" s="11" t="s">
-        <v>83</v>
+      <c r="B137" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="C137" s="9" t="s">
         <v>76</v>
@@ -8794,8 +8794,8 @@
       <c r="A138" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B138" s="9" t="s">
-        <v>76</v>
+      <c r="B138" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>76</v>
@@ -8852,8 +8852,8 @@
       <c r="C141" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D141" s="10" t="s">
-        <v>82</v>
+      <c r="D141" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>76</v>
@@ -8884,8 +8884,8 @@
       <c r="C143" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D143" s="10" t="s">
-        <v>82</v>
+      <c r="D143" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>76</v>
@@ -9026,14 +9026,14 @@
       <c r="C152" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D152" s="11" t="s">
-        <v>83</v>
+      <c r="D152" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F152" s="9" t="s">
-        <v>77</v>
+      <c r="F152" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="153" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9043,8 +9043,8 @@
       <c r="B153" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C153" s="10" t="s">
-        <v>82</v>
+      <c r="C153" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D153" s="9" t="s">
         <v>77</v>
@@ -9052,8 +9052,8 @@
       <c r="E153" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F153" s="15" t="s">
-        <v>101</v>
+      <c r="F153" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="154" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9075,13 +9075,13 @@
       <c r="B155" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C155" s="10" t="s">
-        <v>82</v>
+      <c r="C155" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D155" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E155" s="10" t="s">
+      <c r="E155" s="11" t="s">
         <v>97</v>
       </c>
       <c r="F155" s="9" t="s">
@@ -9185,8 +9185,8 @@
       <c r="B162" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C162" s="9" t="s">
-        <v>78</v>
+      <c r="C162" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D162" s="9" t="s">
         <v>78</v>
@@ -9214,11 +9214,11 @@
       <c r="A164" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B164" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C164" s="9" t="s">
+      <c r="B164" s="9" t="s">
         <v>78</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D164" s="13" t="s">
         <v>93</v>
@@ -9237,8 +9237,8 @@
       <c r="B165" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C165" s="11" t="s">
-        <v>83</v>
+      <c r="C165" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="D165" s="9" t="s">
         <v>78</v>
@@ -9339,14 +9339,14 @@
       <c r="B172" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C172" s="11" t="s">
-        <v>83</v>
+      <c r="C172" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E172" s="13" t="s">
-        <v>93</v>
+      <c r="E172" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>79</v>
@@ -9368,8 +9368,8 @@
       <c r="E173" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F173" s="10" t="s">
-        <v>82</v>
+      <c r="F173" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="174" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9382,14 +9382,14 @@
       <c r="C174" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D174" s="9" t="s">
-        <v>79</v>
+      <c r="D174" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F174" s="10" t="s">
-        <v>82</v>
+      <c r="F174" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9420,8 +9420,8 @@
       <c r="E176" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F176" s="9" t="s">
-        <v>79</v>
+      <c r="F176" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="177" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9440,8 +9440,8 @@
       <c r="E177" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F177" s="9" t="s">
-        <v>79</v>
+      <c r="F177" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="178" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9460,7 +9460,7 @@
       <c r="A179" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B179" s="10" t="s">
+      <c r="B179" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C179" s="9" t="s">
@@ -9612,14 +9612,14 @@
       <c r="A5" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>119</v>
+      <c r="B5" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>121</v>
+      <c r="D5" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>122</v>
@@ -9673,8 +9673,8 @@
       <c r="D8" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>123</v>
+      <c r="E8" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>119</v>
@@ -9688,10 +9688,10 @@
         <v>119</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>124</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>119</v>
@@ -9720,7 +9720,7 @@
         <v>119</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>119</v>
@@ -9795,8 +9795,8 @@
       <c r="D16" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>123</v>
+      <c r="E16" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>126</v>
@@ -9809,8 +9809,8 @@
       <c r="B17" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>120</v>
+      <c r="C17" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>126</v>
@@ -9830,13 +9830,13 @@
         <v>126</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>126</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>126</v>
@@ -9881,14 +9881,14 @@
       <c r="B21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>126</v>
+      <c r="C21" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>126</v>
@@ -9917,7 +9917,7 @@
         <v>126</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>126</v>
@@ -9984,10 +9984,10 @@
         <v>130</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="17" t="s">
         <v>123</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>130</v>
@@ -10004,10 +10004,10 @@
         <v>130</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>131</v>
@@ -10061,8 +10061,8 @@
       <c r="D32" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>130</v>
+      <c r="E32" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>130</v>
@@ -10078,8 +10078,8 @@
       <c r="C33" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>130</v>
+      <c r="D33" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -10104,14 +10104,14 @@
       <c r="A35" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>127</v>
+      <c r="B35" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>130</v>
+      <c r="D35" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -10200,8 +10200,8 @@
       <c r="C41" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="18" t="s">
-        <v>121</v>
+      <c r="D41" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>134</v>
@@ -10218,10 +10218,10 @@
         <v>133</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>133</v>
@@ -10250,13 +10250,13 @@
         <v>133</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E44" s="17" t="s">
-        <v>120</v>
+      <c r="E44" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>133</v>
@@ -10272,8 +10272,8 @@
       <c r="C45" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>133</v>
+      <c r="D45" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>133</v>
@@ -10304,11 +10304,11 @@
       <c r="C47" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" s="9" t="s">
+      <c r="D47" s="9" t="s">
         <v>133</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>133</v>
@@ -10388,8 +10388,8 @@
       <c r="A53" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>137</v>
+      <c r="B53" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>137</v>
@@ -10408,11 +10408,11 @@
       <c r="A54" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>138</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>137</v>
@@ -10444,7 +10444,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>137</v>
@@ -10460,8 +10460,8 @@
       <c r="A57" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="17" t="s">
-        <v>127</v>
+      <c r="B57" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>137</v>
@@ -10499,7 +10499,7 @@
         <v>137</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>137</v>
@@ -10571,8 +10571,8 @@
       <c r="D64" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>141</v>
+      <c r="E64" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>141</v>
@@ -10591,19 +10591,19 @@
       <c r="D65" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E65" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F65" s="9" t="s">
+      <c r="E65" s="9" t="s">
         <v>141</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="17" t="s">
-        <v>127</v>
+      <c r="B66" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>141</v>
@@ -10614,8 +10614,8 @@
       <c r="E66" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F66" s="9" t="s">
-        <v>141</v>
+      <c r="F66" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10634,8 +10634,8 @@
       <c r="A68" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>141</v>
+      <c r="B68" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>141</v>
@@ -10646,8 +10646,8 @@
       <c r="E68" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="F68" s="17" t="s">
-        <v>138</v>
+      <c r="F68" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10666,8 +10666,8 @@
       <c r="E69" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="17" t="s">
-        <v>138</v>
+      <c r="F69" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10759,8 +10759,8 @@
       <c r="B76" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>143</v>
+      <c r="C76" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>143</v>
@@ -10799,14 +10799,14 @@
       <c r="B78" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C78" s="17" t="s">
-        <v>120</v>
+      <c r="C78" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>143</v>
@@ -10828,14 +10828,14 @@
       <c r="A80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="17" t="s">
-        <v>127</v>
+      <c r="B80" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>143</v>
@@ -10851,8 +10851,8 @@
       <c r="B81" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>143</v>
+      <c r="C81" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>143</v>
@@ -10890,7 +10890,7 @@
         <v>143</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>143</v>
@@ -10957,7 +10957,7 @@
         <v>145</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>145</v>
@@ -10973,14 +10973,14 @@
       <c r="B89" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>127</v>
+      <c r="C89" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>145</v>
+        <v>123</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>145</v>
@@ -10993,14 +10993,14 @@
       <c r="B90" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>145</v>
+      <c r="C90" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>145</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>145</v>
@@ -11051,8 +11051,8 @@
       <c r="D93" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E93" s="17" t="s">
-        <v>123</v>
+      <c r="E93" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>145</v>
@@ -11078,7 +11078,7 @@
         <v>145</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>145</v>
@@ -11147,11 +11147,11 @@
       <c r="B100" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D100" s="9" t="s">
+      <c r="C100" s="9" t="s">
         <v>147</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>147</v>
@@ -11167,8 +11167,8 @@
       <c r="B101" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C101" s="17" t="s">
-        <v>138</v>
+      <c r="C101" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>147</v>
@@ -11190,8 +11190,8 @@
       <c r="C102" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D102" s="18" t="s">
-        <v>148</v>
+      <c r="D102" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>147</v>
@@ -11216,8 +11216,8 @@
       <c r="A104" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B104" s="9" t="s">
-        <v>147</v>
+      <c r="B104" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>147</v>
@@ -11228,16 +11228,16 @@
       <c r="E104" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F104" s="17" t="s">
-        <v>149</v>
+      <c r="F104" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B105" s="9" t="s">
-        <v>147</v>
+      <c r="B105" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>147</v>
@@ -11249,7 +11249,7 @@
         <v>122</v>
       </c>
       <c r="F105" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11277,11 +11277,11 @@
       <c r="D107" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E107" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F107" s="9" t="s">
+      <c r="E107" s="9" t="s">
         <v>147</v>
+      </c>
+      <c r="F107" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -11344,8 +11344,8 @@
       <c r="C112" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D112" s="9" t="s">
-        <v>152</v>
+      <c r="D112" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>152</v>
@@ -11358,14 +11358,14 @@
       <c r="A113" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D113" s="17" t="s">
         <v>138</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>152</v>
@@ -11378,14 +11378,14 @@
       <c r="A114" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B114" s="17" t="s">
-        <v>138</v>
+      <c r="B114" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D114" s="18" t="s">
-        <v>148</v>
+      <c r="D114" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>152</v>
@@ -11466,7 +11466,7 @@
         <v>152</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>152</v>
@@ -11536,7 +11536,7 @@
         <v>154</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>154</v>
@@ -11555,8 +11555,8 @@
       <c r="B125" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C125" s="9" t="s">
-        <v>154</v>
+      <c r="C125" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>154</v>
@@ -11578,8 +11578,8 @@
       <c r="C126" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D126" s="18" t="s">
-        <v>148</v>
+      <c r="D126" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>154</v>
@@ -11607,14 +11607,14 @@
       <c r="B128" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C128" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D128" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E128" s="9" t="s">
+      <c r="C128" s="9" t="s">
         <v>154</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E128" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>154</v>
@@ -11636,8 +11636,8 @@
       <c r="E129" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F129" s="9" t="s">
-        <v>154</v>
+      <c r="F129" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="130" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11656,8 +11656,8 @@
       <c r="A131" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B131" s="9" t="s">
-        <v>154</v>
+      <c r="B131" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>154</v>
@@ -11668,8 +11668,8 @@
       <c r="E131" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F131" s="17" t="s">
-        <v>150</v>
+      <c r="F131" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -11746,8 +11746,8 @@
       <c r="A137" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B137" s="17" t="s">
-        <v>127</v>
+      <c r="B137" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="C137" s="9" t="s">
         <v>156</v>
@@ -11766,8 +11766,8 @@
       <c r="A138" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B138" s="9" t="s">
-        <v>156</v>
+      <c r="B138" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>156</v>
@@ -11776,7 +11776,7 @@
         <v>156</v>
       </c>
       <c r="E138" s="17" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F138" s="19" t="s">
         <v>157</v>
@@ -12004,8 +12004,8 @@
       <c r="E152" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F152" s="9" t="s">
-        <v>159</v>
+      <c r="F152" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="153" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12024,8 +12024,8 @@
       <c r="E153" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F153" s="17" t="s">
-        <v>149</v>
+      <c r="F153" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="154" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12157,8 +12157,8 @@
       <c r="B162" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C162" s="9" t="s">
-        <v>162</v>
+      <c r="C162" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D162" s="9" t="s">
         <v>162</v>
@@ -12186,11 +12186,11 @@
       <c r="A164" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B164" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C164" s="17" t="s">
         <v>138</v>
-      </c>
-      <c r="C164" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="D164" s="18" t="s">
         <v>160</v>
@@ -12207,10 +12207,10 @@
         <v>87</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="C165" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="D165" s="9" t="s">
         <v>162</v>
@@ -12312,13 +12312,13 @@
         <v>164</v>
       </c>
       <c r="C172" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E172" s="17" t="s">
-        <v>120</v>
+      <c r="E172" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>164</v>
@@ -12340,8 +12340,8 @@
       <c r="E173" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F173" s="17" t="s">
-        <v>138</v>
+      <c r="F173" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="174" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12354,14 +12354,14 @@
       <c r="C174" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D174" s="9" t="s">
-        <v>164</v>
+      <c r="D174" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F174" s="17" t="s">
-        <v>138</v>
+      <c r="F174" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="175" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12392,8 +12392,8 @@
       <c r="E176" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F176" s="9" t="s">
-        <v>164</v>
+      <c r="F176" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="177" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12412,8 +12412,8 @@
       <c r="E177" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F177" s="9" t="s">
-        <v>164</v>
+      <c r="F177" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="178" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12699,57 +12699,57 @@
       <c r="B196" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C196" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D196" s="21" t="s">
-        <v>168</v>
+      <c r="D196" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="E196" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F196" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="197" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B197" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C197" s="10" t="s">
+      <c r="B197" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C197" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D197" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="E197" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F197" s="10" t="s">
+      <c r="D197" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E197" s="11" t="s">
         <v>182</v>
+      </c>
+      <c r="F197" s="11" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="198" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B198" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C198" s="10" t="s">
+      <c r="B198" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C198" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D198" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E198" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F198" s="11" t="s">
         <v>183</v>
-      </c>
-      <c r="D198" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="E198" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F198" s="10" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="199" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12768,19 +12768,19 @@
       <c r="A200" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B200" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C200" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="D200" s="10" t="s">
+      <c r="C200" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E200" s="10" t="s">
+      <c r="D200" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E200" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="F200" s="10" t="s">
+      <c r="F200" s="11" t="s">
         <v>188</v>
       </c>
     </row>
@@ -12788,19 +12788,19 @@
       <c r="A201" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B201" s="10" t="s">
+      <c r="B201" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="C201" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D201" s="10" t="s">
+      <c r="D201" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E201" s="10" t="s">
+      <c r="E201" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="F201" s="10" t="s">
+      <c r="F201" s="11" t="s">
         <v>188</v>
       </c>
     </row>
@@ -12820,16 +12820,16 @@
       <c r="A203" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B203" s="10" t="s">
+      <c r="B203" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C203" s="10" t="s">
+      <c r="C203" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D203" s="10" t="s">
+      <c r="D203" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E203" s="10" t="s">
+      <c r="E203" s="11" t="s">
         <v>193</v>
       </c>
       <c r="F203" s="22" t="s">
@@ -12893,11 +12893,11 @@
       <c r="B208" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C208" s="11" t="s">
+      <c r="C208" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D208" s="21" t="s">
-        <v>168</v>
+      <c r="D208" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="E208" s="20" t="s">
         <v>169</v>
@@ -12910,14 +12910,14 @@
       <c r="A209" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B209" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="C209" s="11" t="s">
+      <c r="B209" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D209" s="11" t="s">
+      <c r="C209" s="10" t="s">
         <v>200</v>
+      </c>
+      <c r="D209" s="18" t="s">
+        <v>201</v>
       </c>
       <c r="E209" s="20" t="s">
         <v>169</v>
@@ -12930,14 +12930,14 @@
       <c r="A210" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B210" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="C210" s="11" t="s">
+      <c r="B210" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D210" s="11" t="s">
+      <c r="C210" s="10" t="s">
         <v>203</v>
+      </c>
+      <c r="D210" s="21" t="s">
+        <v>168</v>
       </c>
       <c r="E210" s="20" t="s">
         <v>169</v>
@@ -12962,13 +12962,13 @@
       <c r="A212" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B212" s="11" t="s">
+      <c r="B212" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C212" s="11" t="s">
+      <c r="C212" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D212" s="11" t="s">
+      <c r="D212" s="10" t="s">
         <v>206</v>
       </c>
       <c r="E212" s="20" t="s">
@@ -12982,13 +12982,13 @@
       <c r="A213" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B213" s="11" t="s">
+      <c r="B213" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C213" s="11" t="s">
+      <c r="C213" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="D213" s="18" t="s">
+      <c r="D213" s="10" t="s">
         <v>209</v>
       </c>
       <c r="E213" s="20" t="s">
@@ -13014,13 +13014,13 @@
       <c r="A215" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B215" s="11" t="s">
+      <c r="B215" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C215" s="11" t="s">
+      <c r="C215" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D215" s="11" t="s">
+      <c r="D215" s="10" t="s">
         <v>212</v>
       </c>
       <c r="E215" s="20" t="s">
@@ -13093,11 +13093,11 @@
       <c r="D220" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="E220" s="13" t="s">
+      <c r="E220" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F220" s="19" t="s">
         <v>216</v>
-      </c>
-      <c r="F220" s="21" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="221" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13110,14 +13110,14 @@
       <c r="C221" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="D221" s="13" t="s">
-        <v>218</v>
+      <c r="D221" s="18" t="s">
+        <v>201</v>
       </c>
       <c r="E221" s="21" t="s">
         <v>168</v>
       </c>
       <c r="F221" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="222" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13128,16 +13128,16 @@
         <v>169</v>
       </c>
       <c r="C222" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D222" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="D222" s="13" t="s">
+      <c r="E222" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="E222" s="13" t="s">
+      <c r="F222" s="13" t="s">
         <v>222</v>
-      </c>
-      <c r="F222" s="13" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="223" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13160,16 +13160,16 @@
         <v>169</v>
       </c>
       <c r="C224" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D224" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D224" s="13" t="s">
+      <c r="E224" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="E224" s="13" t="s">
+      <c r="F224" s="13" t="s">
         <v>226</v>
-      </c>
-      <c r="F224" s="13" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="225" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13179,11 +13179,11 @@
       <c r="B225" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="C225" s="19" t="s">
+      <c r="C225" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D225" s="13" t="s">
         <v>228</v>
-      </c>
-      <c r="D225" s="18" t="s">
-        <v>209</v>
       </c>
       <c r="E225" s="13" t="s">
         <v>229</v>
@@ -13284,11 +13284,11 @@
       <c r="C232" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D232" s="14" t="s">
+      <c r="D232" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E232" s="14" t="s">
         <v>236</v>
-      </c>
-      <c r="E232" s="14" t="s">
-        <v>237</v>
       </c>
       <c r="F232" s="20" t="s">
         <v>169</v>
@@ -13304,11 +13304,11 @@
       <c r="C233" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D233" s="14" t="s">
-        <v>238</v>
+      <c r="D233" s="18" t="s">
+        <v>201</v>
       </c>
       <c r="E233" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F233" s="20" t="s">
         <v>169</v>
@@ -13324,11 +13324,11 @@
       <c r="C234" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D234" s="21" t="s">
-        <v>168</v>
+      <c r="D234" s="14" t="s">
+        <v>238</v>
       </c>
       <c r="E234" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F234" s="20" t="s">
         <v>169</v>
@@ -13357,10 +13357,10 @@
         <v>169</v>
       </c>
       <c r="D236" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E236" s="14" t="s">
         <v>241</v>
-      </c>
-      <c r="E236" s="14" t="s">
-        <v>242</v>
       </c>
       <c r="F236" s="20" t="s">
         <v>169</v>
@@ -13376,8 +13376,8 @@
       <c r="C237" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D237" s="18" t="s">
-        <v>209</v>
+      <c r="D237" s="14" t="s">
+        <v>242</v>
       </c>
       <c r="E237" s="14" t="s">
         <v>243</v>
@@ -13482,7 +13482,7 @@
         <v>169</v>
       </c>
       <c r="E244" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F244" s="21" t="s">
         <v>168</v>

--- a/Tapping_S2_Specialist_Timetable.xlsx
+++ b/Tapping_S2_Specialist_Timetable.xlsx
@@ -3103,7 +3103,7 @@
     <t>| Natalie Carter | PBS | Mon P1 | fixed (moved from Mon P3 so LA23 can take P3 - Brad item 5) |</t>
   </si>
   <si>
-    <t>| Cheryl Peak | Events | Fri P1 | leads the Friday assembly (P1 carries no specialist teaching) |</t>
+    <t>| Cheryl Peak | Events | Thu P1 | Peak non-teaching block |</t>
   </si>
   <si>
     <t>| Lincoln Rose | SSTUWA | Fri P2 | LA9 covered by Aaron Bell (Health) · additional 45-min release on top of normal DOTT |</t>
@@ -13093,11 +13093,11 @@
       <c r="D220" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="E220" s="21" t="s">
+      <c r="E220" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F220" s="21" t="s">
         <v>168</v>
-      </c>
-      <c r="F220" s="19" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="221" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
